--- a/030-試験/031-単体試験計画書兼結果書（ItemsDAO）.xlsx
+++ b/030-試験/031-単体試験計画書兼結果書（ItemsDAO）.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\システム開発演習\030-試験\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6056ABE0-37AF-43B9-AFB0-BD449B3769B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E56EC6A0-1132-4D0D-9C99-5341F3FD855B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{A6033112-71BA-4037-88EF-FEBDF2F3FF10}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{A6033112-71BA-4037-88EF-FEBDF2F3FF10}"/>
   </bookViews>
   <sheets>
     <sheet name="単体テスト_前提条件" sheetId="4" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="697" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="695" uniqueCount="189">
   <si>
     <t>ItemsDAO</t>
     <phoneticPr fontId="5"/>
@@ -1085,18 +1085,6 @@
     <t>表示されていること</t>
   </si>
   <si>
-    <t>「org.postgresql.util.</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>PSQLException: クエリは結果</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>を返却しませんでした。」</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
     <t>されているか確認する</t>
   </si>
   <si>
@@ -1206,10 +1194,6 @@
     <phoneticPr fontId="5"/>
   </si>
   <si>
-    <t>と表示されている</t>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
     <t>OK</t>
     <phoneticPr fontId="5"/>
   </si>
@@ -1218,6 +1202,13 @@
     <rPh sb="0" eb="4">
       <t>スズキタカユキ</t>
     </rPh>
+    <phoneticPr fontId="5"/>
+  </si>
+  <si>
+    <t>と表示されている</t>
+  </si>
+  <si>
+    <t>「SQLExceptionが発生しました」</t>
     <phoneticPr fontId="5"/>
   </si>
 </sst>
@@ -1944,6 +1935,54 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="4" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1983,54 +2022,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2057,57 +2048,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2136,6 +2076,63 @@
     <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2146,6 +2143,24 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2165,30 +2180,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2522,130 +2513,130 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:72" ht="15" customHeight="1" thickTop="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="120"/>
-      <c r="C1" s="120"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="120"/>
-      <c r="F1" s="120"/>
-      <c r="G1" s="120"/>
-      <c r="H1" s="120"/>
-      <c r="I1" s="120"/>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="120"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="120"/>
-      <c r="R1" s="121"/>
-      <c r="S1" s="109" t="s">
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
+      <c r="I1" s="107"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="105" t="s">
         <v>15</v>
       </c>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
-      <c r="V1" s="109"/>
-      <c r="W1" s="118"/>
-      <c r="X1" s="118"/>
-      <c r="Y1" s="118"/>
-      <c r="Z1" s="118"/>
-      <c r="AA1" s="118"/>
-      <c r="AB1" s="118"/>
-      <c r="AC1" s="118"/>
-      <c r="AD1" s="118"/>
-      <c r="AE1" s="118"/>
-      <c r="AF1" s="118"/>
-      <c r="AG1" s="109" t="s">
+      <c r="T1" s="105"/>
+      <c r="U1" s="105"/>
+      <c r="V1" s="105"/>
+      <c r="W1" s="104"/>
+      <c r="X1" s="104"/>
+      <c r="Y1" s="104"/>
+      <c r="Z1" s="104"/>
+      <c r="AA1" s="104"/>
+      <c r="AB1" s="104"/>
+      <c r="AC1" s="104"/>
+      <c r="AD1" s="104"/>
+      <c r="AE1" s="104"/>
+      <c r="AF1" s="104"/>
+      <c r="AG1" s="105" t="s">
         <v>14</v>
       </c>
-      <c r="AH1" s="109"/>
-      <c r="AI1" s="109"/>
-      <c r="AJ1" s="109"/>
-      <c r="AK1" s="96">
+      <c r="AH1" s="105"/>
+      <c r="AI1" s="105"/>
+      <c r="AJ1" s="105"/>
+      <c r="AK1" s="112">
         <v>45574</v>
       </c>
-      <c r="AL1" s="96"/>
-      <c r="AM1" s="96"/>
-      <c r="AN1" s="96"/>
-      <c r="AO1" s="96"/>
-      <c r="AP1" s="96"/>
-      <c r="AQ1" s="96"/>
-      <c r="AR1" s="96"/>
-      <c r="AS1" s="96"/>
-      <c r="AT1" s="96"/>
-      <c r="AU1" s="97" t="s">
+      <c r="AL1" s="112"/>
+      <c r="AM1" s="112"/>
+      <c r="AN1" s="112"/>
+      <c r="AO1" s="112"/>
+      <c r="AP1" s="112"/>
+      <c r="AQ1" s="112"/>
+      <c r="AR1" s="112"/>
+      <c r="AS1" s="112"/>
+      <c r="AT1" s="112"/>
+      <c r="AU1" s="113" t="s">
         <v>13</v>
       </c>
-      <c r="AV1" s="98"/>
-      <c r="AW1" s="101"/>
-      <c r="AX1" s="102"/>
-      <c r="AY1" s="102"/>
-      <c r="AZ1" s="103"/>
+      <c r="AV1" s="114"/>
+      <c r="AW1" s="117"/>
+      <c r="AX1" s="118"/>
+      <c r="AY1" s="118"/>
+      <c r="AZ1" s="119"/>
     </row>
     <row r="2" spans="1:72" ht="15" customHeight="1" thickBot="1">
-      <c r="A2" s="122"/>
-      <c r="B2" s="123"/>
-      <c r="C2" s="123"/>
-      <c r="D2" s="123"/>
-      <c r="E2" s="123"/>
-      <c r="F2" s="123"/>
-      <c r="G2" s="123"/>
-      <c r="H2" s="123"/>
-      <c r="I2" s="123"/>
-      <c r="J2" s="123"/>
-      <c r="K2" s="123"/>
-      <c r="L2" s="123"/>
-      <c r="M2" s="123"/>
-      <c r="N2" s="123"/>
-      <c r="O2" s="123"/>
-      <c r="P2" s="123"/>
-      <c r="Q2" s="123"/>
-      <c r="R2" s="124"/>
-      <c r="S2" s="107" t="s">
+      <c r="A2" s="109"/>
+      <c r="B2" s="110"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="110"/>
+      <c r="E2" s="110"/>
+      <c r="F2" s="110"/>
+      <c r="G2" s="110"/>
+      <c r="H2" s="110"/>
+      <c r="I2" s="110"/>
+      <c r="J2" s="110"/>
+      <c r="K2" s="110"/>
+      <c r="L2" s="110"/>
+      <c r="M2" s="110"/>
+      <c r="N2" s="110"/>
+      <c r="O2" s="110"/>
+      <c r="P2" s="110"/>
+      <c r="Q2" s="110"/>
+      <c r="R2" s="111"/>
+      <c r="S2" s="123" t="s">
         <v>12</v>
       </c>
-      <c r="T2" s="107"/>
-      <c r="U2" s="107"/>
-      <c r="V2" s="107"/>
-      <c r="W2" s="108" t="s">
+      <c r="T2" s="123"/>
+      <c r="U2" s="123"/>
+      <c r="V2" s="123"/>
+      <c r="W2" s="124" t="s">
         <v>11</v>
       </c>
-      <c r="X2" s="108"/>
-      <c r="Y2" s="108"/>
-      <c r="Z2" s="108"/>
-      <c r="AA2" s="108"/>
-      <c r="AB2" s="108"/>
-      <c r="AC2" s="108"/>
-      <c r="AD2" s="108"/>
-      <c r="AE2" s="108"/>
-      <c r="AF2" s="108"/>
-      <c r="AG2" s="107" t="s">
+      <c r="X2" s="124"/>
+      <c r="Y2" s="124"/>
+      <c r="Z2" s="124"/>
+      <c r="AA2" s="124"/>
+      <c r="AB2" s="124"/>
+      <c r="AC2" s="124"/>
+      <c r="AD2" s="124"/>
+      <c r="AE2" s="124"/>
+      <c r="AF2" s="124"/>
+      <c r="AG2" s="123" t="s">
         <v>10</v>
       </c>
-      <c r="AH2" s="107"/>
-      <c r="AI2" s="107"/>
-      <c r="AJ2" s="107"/>
-      <c r="AK2" s="108" t="s">
+      <c r="AH2" s="123"/>
+      <c r="AI2" s="123"/>
+      <c r="AJ2" s="123"/>
+      <c r="AK2" s="124" t="s">
         <v>28</v>
       </c>
-      <c r="AL2" s="108"/>
-      <c r="AM2" s="108"/>
-      <c r="AN2" s="108"/>
-      <c r="AO2" s="108"/>
-      <c r="AP2" s="108"/>
-      <c r="AQ2" s="108"/>
-      <c r="AR2" s="108"/>
-      <c r="AS2" s="108"/>
-      <c r="AT2" s="108"/>
-      <c r="AU2" s="99"/>
-      <c r="AV2" s="100"/>
-      <c r="AW2" s="104"/>
-      <c r="AX2" s="105"/>
-      <c r="AY2" s="105"/>
-      <c r="AZ2" s="106"/>
+      <c r="AL2" s="124"/>
+      <c r="AM2" s="124"/>
+      <c r="AN2" s="124"/>
+      <c r="AO2" s="124"/>
+      <c r="AP2" s="124"/>
+      <c r="AQ2" s="124"/>
+      <c r="AR2" s="124"/>
+      <c r="AS2" s="124"/>
+      <c r="AT2" s="124"/>
+      <c r="AU2" s="115"/>
+      <c r="AV2" s="116"/>
+      <c r="AW2" s="120"/>
+      <c r="AX2" s="121"/>
+      <c r="AY2" s="121"/>
+      <c r="AZ2" s="122"/>
     </row>
     <row r="3" spans="1:72" ht="15" customHeight="1" thickTop="1">
       <c r="B3" s="31"/>
@@ -2715,54 +2706,54 @@
       <c r="BT4" s="41"/>
     </row>
     <row r="5" spans="1:72" ht="15" customHeight="1">
-      <c r="A5" s="116" t="s">
+      <c r="A5" s="102" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="116"/>
-      <c r="C5" s="116"/>
-      <c r="D5" s="116"/>
-      <c r="E5" s="110" t="s">
+      <c r="B5" s="102"/>
+      <c r="C5" s="102"/>
+      <c r="D5" s="102"/>
+      <c r="E5" s="96" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="111"/>
-      <c r="G5" s="111"/>
-      <c r="H5" s="111"/>
-      <c r="I5" s="111"/>
-      <c r="J5" s="111"/>
-      <c r="K5" s="111"/>
-      <c r="L5" s="111"/>
-      <c r="M5" s="111"/>
-      <c r="N5" s="111"/>
-      <c r="O5" s="111"/>
-      <c r="P5" s="111"/>
-      <c r="Q5" s="111"/>
-      <c r="R5" s="111"/>
-      <c r="S5" s="111"/>
-      <c r="T5" s="111"/>
-      <c r="U5" s="112"/>
+      <c r="F5" s="97"/>
+      <c r="G5" s="97"/>
+      <c r="H5" s="97"/>
+      <c r="I5" s="97"/>
+      <c r="J5" s="97"/>
+      <c r="K5" s="97"/>
+      <c r="L5" s="97"/>
+      <c r="M5" s="97"/>
+      <c r="N5" s="97"/>
+      <c r="O5" s="97"/>
+      <c r="P5" s="97"/>
+      <c r="Q5" s="97"/>
+      <c r="R5" s="97"/>
+      <c r="S5" s="97"/>
+      <c r="T5" s="97"/>
+      <c r="U5" s="98"/>
     </row>
     <row r="6" spans="1:72" ht="15" customHeight="1">
-      <c r="A6" s="117"/>
-      <c r="B6" s="117"/>
-      <c r="C6" s="117"/>
-      <c r="D6" s="117"/>
-      <c r="E6" s="113"/>
-      <c r="F6" s="114"/>
-      <c r="G6" s="114"/>
-      <c r="H6" s="114"/>
-      <c r="I6" s="114"/>
-      <c r="J6" s="114"/>
-      <c r="K6" s="114"/>
-      <c r="L6" s="114"/>
-      <c r="M6" s="114"/>
-      <c r="N6" s="114"/>
-      <c r="O6" s="114"/>
-      <c r="P6" s="114"/>
-      <c r="Q6" s="114"/>
-      <c r="R6" s="114"/>
-      <c r="S6" s="114"/>
-      <c r="T6" s="114"/>
-      <c r="U6" s="115"/>
+      <c r="A6" s="103"/>
+      <c r="B6" s="103"/>
+      <c r="C6" s="103"/>
+      <c r="D6" s="103"/>
+      <c r="E6" s="99"/>
+      <c r="F6" s="100"/>
+      <c r="G6" s="100"/>
+      <c r="H6" s="100"/>
+      <c r="I6" s="100"/>
+      <c r="J6" s="100"/>
+      <c r="K6" s="100"/>
+      <c r="L6" s="100"/>
+      <c r="M6" s="100"/>
+      <c r="N6" s="100"/>
+      <c r="O6" s="100"/>
+      <c r="P6" s="100"/>
+      <c r="Q6" s="100"/>
+      <c r="R6" s="100"/>
+      <c r="S6" s="100"/>
+      <c r="T6" s="100"/>
+      <c r="U6" s="101"/>
     </row>
     <row r="7" spans="1:72" ht="15" customHeight="1">
       <c r="A7" s="54">
@@ -4838,7 +4829,7 @@
       <c r="C83" s="55"/>
       <c r="D83" s="56"/>
       <c r="E83" s="54" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F83" s="55"/>
       <c r="G83" s="55"/>
@@ -4863,7 +4854,7 @@
       <c r="C84" s="51"/>
       <c r="D84" s="57"/>
       <c r="E84" s="50" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F84" s="51"/>
       <c r="G84" s="51"/>
@@ -4888,7 +4879,7 @@
       <c r="C85" s="51"/>
       <c r="D85" s="57"/>
       <c r="E85" s="50" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F85" s="51"/>
       <c r="G85" s="51"/>
@@ -4913,7 +4904,7 @@
       <c r="C86" s="51"/>
       <c r="D86" s="57"/>
       <c r="E86" s="50" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F86" s="51"/>
       <c r="G86" s="51"/>
@@ -4938,7 +4929,7 @@
       <c r="C87" s="51"/>
       <c r="D87" s="57"/>
       <c r="E87" s="50" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F87" s="51"/>
       <c r="G87" s="51"/>
@@ -4965,7 +4956,7 @@
       <c r="C88" s="55"/>
       <c r="D88" s="56"/>
       <c r="E88" s="54" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F88" s="55"/>
       <c r="G88" s="55"/>
@@ -4990,7 +4981,7 @@
       <c r="C89" s="51"/>
       <c r="D89" s="57"/>
       <c r="E89" s="50" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F89" s="51"/>
       <c r="G89" s="51"/>
@@ -5015,7 +5006,7 @@
       <c r="C90" s="51"/>
       <c r="D90" s="57"/>
       <c r="E90" s="50" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F90" s="51"/>
       <c r="G90" s="51"/>
@@ -5040,7 +5031,7 @@
       <c r="C91" s="51"/>
       <c r="D91" s="57"/>
       <c r="E91" s="50" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F91" s="51"/>
       <c r="G91" s="51"/>
@@ -5065,7 +5056,7 @@
       <c r="C92" s="53"/>
       <c r="D92" s="58"/>
       <c r="E92" s="52" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F92" s="53"/>
       <c r="G92" s="53"/>
@@ -5092,7 +5083,7 @@
       <c r="C93" s="55"/>
       <c r="D93" s="56"/>
       <c r="E93" s="54" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F93" s="55"/>
       <c r="G93" s="55"/>
@@ -5117,7 +5108,7 @@
       <c r="C94" s="51"/>
       <c r="D94" s="57"/>
       <c r="E94" s="50" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F94" s="51"/>
       <c r="G94" s="51"/>
@@ -5142,7 +5133,7 @@
       <c r="C95" s="51"/>
       <c r="D95" s="57"/>
       <c r="E95" s="50" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F95" s="51"/>
       <c r="G95" s="51"/>
@@ -5167,7 +5158,7 @@
       <c r="C96" s="51"/>
       <c r="D96" s="57"/>
       <c r="E96" s="50" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F96" s="51"/>
       <c r="G96" s="51"/>
@@ -5192,7 +5183,7 @@
       <c r="C97" s="53"/>
       <c r="D97" s="58"/>
       <c r="E97" s="52" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F97" s="53"/>
       <c r="G97" s="53"/>
@@ -5219,7 +5210,7 @@
       <c r="C98" s="55"/>
       <c r="D98" s="56"/>
       <c r="E98" s="54" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F98" s="55"/>
       <c r="G98" s="55"/>
@@ -5244,7 +5235,7 @@
       <c r="C99" s="51"/>
       <c r="D99" s="57"/>
       <c r="E99" s="50" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F99" s="51"/>
       <c r="G99" s="51"/>
@@ -5269,7 +5260,7 @@
       <c r="C100" s="51"/>
       <c r="D100" s="57"/>
       <c r="E100" s="50" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F100" s="51"/>
       <c r="G100" s="51"/>
@@ -5294,7 +5285,7 @@
       <c r="C101" s="51"/>
       <c r="D101" s="57"/>
       <c r="E101" s="50" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F101" s="51"/>
       <c r="G101" s="51"/>
@@ -5319,7 +5310,7 @@
       <c r="C102" s="53"/>
       <c r="D102" s="58"/>
       <c r="E102" s="52" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F102" s="53"/>
       <c r="G102" s="53"/>
@@ -5346,7 +5337,7 @@
       <c r="C103" s="55"/>
       <c r="D103" s="56"/>
       <c r="E103" s="54" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F103" s="55"/>
       <c r="G103" s="55"/>
@@ -5371,7 +5362,7 @@
       <c r="C104" s="51"/>
       <c r="D104" s="57"/>
       <c r="E104" s="50" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F104" s="51"/>
       <c r="G104" s="51"/>
@@ -5396,7 +5387,7 @@
       <c r="C105" s="51"/>
       <c r="D105" s="57"/>
       <c r="E105" s="50" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F105" s="51"/>
       <c r="G105" s="51"/>
@@ -5421,7 +5412,7 @@
       <c r="C106" s="51"/>
       <c r="D106" s="57"/>
       <c r="E106" s="50" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F106" s="51"/>
       <c r="G106" s="51"/>
@@ -5446,7 +5437,7 @@
       <c r="C107" s="53"/>
       <c r="D107" s="58"/>
       <c r="E107" s="52" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F107" s="53"/>
       <c r="G107" s="53"/>
@@ -7054,11 +7045,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="E5:U6"/>
-    <mergeCell ref="A5:D6"/>
-    <mergeCell ref="W1:AF1"/>
-    <mergeCell ref="AG1:AJ1"/>
-    <mergeCell ref="A1:R2"/>
     <mergeCell ref="AK1:AT1"/>
     <mergeCell ref="AU1:AV2"/>
     <mergeCell ref="AW1:AZ2"/>
@@ -7067,6 +7053,11 @@
     <mergeCell ref="AG2:AJ2"/>
     <mergeCell ref="AK2:AT2"/>
     <mergeCell ref="S1:V1"/>
+    <mergeCell ref="E5:U6"/>
+    <mergeCell ref="A5:D6"/>
+    <mergeCell ref="W1:AF1"/>
+    <mergeCell ref="AG1:AJ1"/>
+    <mergeCell ref="A1:R2"/>
   </mergeCells>
   <phoneticPr fontId="5"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7083,142 +7074,142 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:73" customFormat="1" ht="15" customHeight="1" thickTop="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="120"/>
-      <c r="C1" s="120"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="120"/>
-      <c r="F1" s="120"/>
-      <c r="G1" s="120"/>
-      <c r="H1" s="120"/>
-      <c r="I1" s="120"/>
-      <c r="J1" s="120"/>
-      <c r="K1" s="120"/>
-      <c r="L1" s="120"/>
-      <c r="M1" s="120"/>
-      <c r="N1" s="120"/>
-      <c r="O1" s="120"/>
-      <c r="P1" s="120"/>
-      <c r="Q1" s="120"/>
-      <c r="R1" s="121"/>
-      <c r="S1" s="109" t="s">
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="107"/>
+      <c r="H1" s="107"/>
+      <c r="I1" s="107"/>
+      <c r="J1" s="107"/>
+      <c r="K1" s="107"/>
+      <c r="L1" s="107"/>
+      <c r="M1" s="107"/>
+      <c r="N1" s="107"/>
+      <c r="O1" s="107"/>
+      <c r="P1" s="107"/>
+      <c r="Q1" s="107"/>
+      <c r="R1" s="108"/>
+      <c r="S1" s="105" t="s">
         <v>15</v>
       </c>
-      <c r="T1" s="109"/>
-      <c r="U1" s="109"/>
-      <c r="V1" s="109"/>
-      <c r="W1" s="109"/>
-      <c r="X1" s="109"/>
-      <c r="Y1" s="109"/>
-      <c r="Z1" s="109"/>
-      <c r="AA1" s="109"/>
-      <c r="AB1" s="109"/>
-      <c r="AC1" s="118"/>
-      <c r="AD1" s="118"/>
-      <c r="AE1" s="118"/>
-      <c r="AF1" s="118"/>
-      <c r="AG1" s="118"/>
-      <c r="AH1" s="118"/>
-      <c r="AI1" s="118"/>
-      <c r="AJ1" s="118"/>
-      <c r="AK1" s="118"/>
-      <c r="AL1" s="118"/>
-      <c r="AM1" s="109" t="s">
+      <c r="T1" s="105"/>
+      <c r="U1" s="105"/>
+      <c r="V1" s="105"/>
+      <c r="W1" s="105"/>
+      <c r="X1" s="105"/>
+      <c r="Y1" s="105"/>
+      <c r="Z1" s="105"/>
+      <c r="AA1" s="105"/>
+      <c r="AB1" s="105"/>
+      <c r="AC1" s="104"/>
+      <c r="AD1" s="104"/>
+      <c r="AE1" s="104"/>
+      <c r="AF1" s="104"/>
+      <c r="AG1" s="104"/>
+      <c r="AH1" s="104"/>
+      <c r="AI1" s="104"/>
+      <c r="AJ1" s="104"/>
+      <c r="AK1" s="104"/>
+      <c r="AL1" s="104"/>
+      <c r="AM1" s="105" t="s">
         <v>14</v>
       </c>
-      <c r="AN1" s="109"/>
-      <c r="AO1" s="109"/>
-      <c r="AP1" s="109"/>
-      <c r="AQ1" s="96">
-        <v>45574</v>
-      </c>
-      <c r="AR1" s="96"/>
-      <c r="AS1" s="96"/>
-      <c r="AT1" s="96"/>
-      <c r="AU1" s="96"/>
-      <c r="AV1" s="96"/>
-      <c r="AW1" s="96"/>
-      <c r="AX1" s="96"/>
-      <c r="AY1" s="96"/>
-      <c r="AZ1" s="96"/>
-      <c r="BA1" s="97" t="s">
+      <c r="AN1" s="105"/>
+      <c r="AO1" s="105"/>
+      <c r="AP1" s="105"/>
+      <c r="AQ1" s="112">
+        <v>45586</v>
+      </c>
+      <c r="AR1" s="112"/>
+      <c r="AS1" s="112"/>
+      <c r="AT1" s="112"/>
+      <c r="AU1" s="112"/>
+      <c r="AV1" s="112"/>
+      <c r="AW1" s="112"/>
+      <c r="AX1" s="112"/>
+      <c r="AY1" s="112"/>
+      <c r="AZ1" s="112"/>
+      <c r="BA1" s="113" t="s">
         <v>13</v>
       </c>
-      <c r="BB1" s="98"/>
-      <c r="BC1" s="101"/>
-      <c r="BD1" s="102"/>
-      <c r="BE1" s="102"/>
-      <c r="BF1" s="103"/>
+      <c r="BB1" s="114"/>
+      <c r="BC1" s="117"/>
+      <c r="BD1" s="118"/>
+      <c r="BE1" s="118"/>
+      <c r="BF1" s="119"/>
     </row>
     <row r="2" spans="1:73" customFormat="1" ht="15" customHeight="1" thickBot="1">
-      <c r="A2" s="122"/>
-      <c r="B2" s="123"/>
-      <c r="C2" s="123"/>
-      <c r="D2" s="123"/>
-      <c r="E2" s="123"/>
-      <c r="F2" s="123"/>
-      <c r="G2" s="123"/>
-      <c r="H2" s="123"/>
-      <c r="I2" s="123"/>
-      <c r="J2" s="123"/>
-      <c r="K2" s="123"/>
-      <c r="L2" s="123"/>
-      <c r="M2" s="123"/>
-      <c r="N2" s="123"/>
-      <c r="O2" s="123"/>
-      <c r="P2" s="123"/>
-      <c r="Q2" s="123"/>
-      <c r="R2" s="124"/>
-      <c r="S2" s="107" t="s">
+      <c r="A2" s="109"/>
+      <c r="B2" s="110"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="110"/>
+      <c r="E2" s="110"/>
+      <c r="F2" s="110"/>
+      <c r="G2" s="110"/>
+      <c r="H2" s="110"/>
+      <c r="I2" s="110"/>
+      <c r="J2" s="110"/>
+      <c r="K2" s="110"/>
+      <c r="L2" s="110"/>
+      <c r="M2" s="110"/>
+      <c r="N2" s="110"/>
+      <c r="O2" s="110"/>
+      <c r="P2" s="110"/>
+      <c r="Q2" s="110"/>
+      <c r="R2" s="111"/>
+      <c r="S2" s="123" t="s">
         <v>12</v>
       </c>
-      <c r="T2" s="107"/>
-      <c r="U2" s="107"/>
-      <c r="V2" s="107"/>
-      <c r="W2" s="107"/>
-      <c r="X2" s="107"/>
-      <c r="Y2" s="107"/>
-      <c r="Z2" s="107"/>
-      <c r="AA2" s="107"/>
-      <c r="AB2" s="107"/>
-      <c r="AC2" s="108" t="s">
+      <c r="T2" s="123"/>
+      <c r="U2" s="123"/>
+      <c r="V2" s="123"/>
+      <c r="W2" s="123"/>
+      <c r="X2" s="123"/>
+      <c r="Y2" s="123"/>
+      <c r="Z2" s="123"/>
+      <c r="AA2" s="123"/>
+      <c r="AB2" s="123"/>
+      <c r="AC2" s="124" t="s">
         <v>11</v>
       </c>
-      <c r="AD2" s="108"/>
-      <c r="AE2" s="108"/>
-      <c r="AF2" s="108"/>
-      <c r="AG2" s="108"/>
-      <c r="AH2" s="108"/>
-      <c r="AI2" s="108"/>
-      <c r="AJ2" s="108"/>
-      <c r="AK2" s="108"/>
-      <c r="AL2" s="108"/>
-      <c r="AM2" s="107" t="s">
+      <c r="AD2" s="124"/>
+      <c r="AE2" s="124"/>
+      <c r="AF2" s="124"/>
+      <c r="AG2" s="124"/>
+      <c r="AH2" s="124"/>
+      <c r="AI2" s="124"/>
+      <c r="AJ2" s="124"/>
+      <c r="AK2" s="124"/>
+      <c r="AL2" s="124"/>
+      <c r="AM2" s="123" t="s">
         <v>10</v>
       </c>
-      <c r="AN2" s="107"/>
-      <c r="AO2" s="107"/>
-      <c r="AP2" s="107"/>
-      <c r="AQ2" s="108" t="s">
+      <c r="AN2" s="123"/>
+      <c r="AO2" s="123"/>
+      <c r="AP2" s="123"/>
+      <c r="AQ2" s="124" t="s">
         <v>28</v>
       </c>
-      <c r="AR2" s="108"/>
-      <c r="AS2" s="108"/>
-      <c r="AT2" s="108"/>
-      <c r="AU2" s="108"/>
-      <c r="AV2" s="108"/>
-      <c r="AW2" s="108"/>
-      <c r="AX2" s="108"/>
-      <c r="AY2" s="108"/>
-      <c r="AZ2" s="108"/>
-      <c r="BA2" s="99"/>
-      <c r="BB2" s="100"/>
-      <c r="BC2" s="104"/>
-      <c r="BD2" s="105"/>
-      <c r="BE2" s="105"/>
-      <c r="BF2" s="106"/>
+      <c r="AR2" s="124"/>
+      <c r="AS2" s="124"/>
+      <c r="AT2" s="124"/>
+      <c r="AU2" s="124"/>
+      <c r="AV2" s="124"/>
+      <c r="AW2" s="124"/>
+      <c r="AX2" s="124"/>
+      <c r="AY2" s="124"/>
+      <c r="AZ2" s="124"/>
+      <c r="BA2" s="115"/>
+      <c r="BB2" s="116"/>
+      <c r="BC2" s="120"/>
+      <c r="BD2" s="121"/>
+      <c r="BE2" s="121"/>
+      <c r="BF2" s="122"/>
     </row>
     <row r="3" spans="1:73" ht="15" customHeight="1" thickTop="1"/>
     <row r="4" spans="1:73" ht="15" customHeight="1">
@@ -7282,180 +7273,180 @@
       <c r="BF4" s="23"/>
     </row>
     <row r="5" spans="1:73" s="22" customFormat="1" ht="15" customHeight="1">
-      <c r="A5" s="134" t="s">
+      <c r="A5" s="153" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="134"/>
-      <c r="C5" s="134" t="s">
+      <c r="B5" s="153"/>
+      <c r="C5" s="153" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="134"/>
-      <c r="E5" s="134"/>
-      <c r="F5" s="134"/>
-      <c r="G5" s="148" t="s">
+      <c r="D5" s="153"/>
+      <c r="E5" s="153"/>
+      <c r="F5" s="153"/>
+      <c r="G5" s="150" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="149"/>
-      <c r="I5" s="149"/>
-      <c r="J5" s="149"/>
-      <c r="K5" s="149"/>
-      <c r="L5" s="149"/>
-      <c r="M5" s="149"/>
-      <c r="N5" s="149"/>
-      <c r="O5" s="149"/>
-      <c r="P5" s="149"/>
-      <c r="Q5" s="149"/>
-      <c r="R5" s="149"/>
-      <c r="S5" s="149"/>
-      <c r="T5" s="150"/>
-      <c r="U5" s="137" t="s">
+      <c r="H5" s="151"/>
+      <c r="I5" s="151"/>
+      <c r="J5" s="151"/>
+      <c r="K5" s="151"/>
+      <c r="L5" s="151"/>
+      <c r="M5" s="151"/>
+      <c r="N5" s="151"/>
+      <c r="O5" s="151"/>
+      <c r="P5" s="151"/>
+      <c r="Q5" s="151"/>
+      <c r="R5" s="151"/>
+      <c r="S5" s="151"/>
+      <c r="T5" s="152"/>
+      <c r="U5" s="155" t="s">
         <v>105</v>
       </c>
-      <c r="V5" s="137"/>
-      <c r="W5" s="137"/>
-      <c r="X5" s="137"/>
-      <c r="Y5" s="137"/>
-      <c r="Z5" s="138"/>
-      <c r="AA5" s="136" t="s">
+      <c r="V5" s="155"/>
+      <c r="W5" s="155"/>
+      <c r="X5" s="155"/>
+      <c r="Y5" s="155"/>
+      <c r="Z5" s="156"/>
+      <c r="AA5" s="154" t="s">
         <v>17</v>
       </c>
-      <c r="AB5" s="137"/>
-      <c r="AC5" s="137"/>
-      <c r="AD5" s="137"/>
-      <c r="AE5" s="137"/>
-      <c r="AF5" s="137"/>
-      <c r="AG5" s="137"/>
-      <c r="AH5" s="137"/>
-      <c r="AI5" s="137"/>
-      <c r="AJ5" s="137"/>
-      <c r="AK5" s="137"/>
-      <c r="AL5" s="137"/>
-      <c r="AM5" s="137"/>
-      <c r="AN5" s="138"/>
-      <c r="AO5" s="142" t="s">
+      <c r="AB5" s="155"/>
+      <c r="AC5" s="155"/>
+      <c r="AD5" s="155"/>
+      <c r="AE5" s="155"/>
+      <c r="AF5" s="155"/>
+      <c r="AG5" s="155"/>
+      <c r="AH5" s="155"/>
+      <c r="AI5" s="155"/>
+      <c r="AJ5" s="155"/>
+      <c r="AK5" s="155"/>
+      <c r="AL5" s="155"/>
+      <c r="AM5" s="155"/>
+      <c r="AN5" s="156"/>
+      <c r="AO5" s="143" t="s">
         <v>7</v>
       </c>
-      <c r="AP5" s="143"/>
-      <c r="AQ5" s="143"/>
-      <c r="AR5" s="143"/>
-      <c r="AS5" s="143"/>
-      <c r="AT5" s="143"/>
-      <c r="AU5" s="143"/>
-      <c r="AV5" s="143"/>
-      <c r="AW5" s="143"/>
-      <c r="AX5" s="143"/>
-      <c r="AY5" s="143"/>
-      <c r="AZ5" s="144"/>
-      <c r="BA5" s="142" t="s">
+      <c r="AP5" s="144"/>
+      <c r="AQ5" s="144"/>
+      <c r="AR5" s="144"/>
+      <c r="AS5" s="144"/>
+      <c r="AT5" s="144"/>
+      <c r="AU5" s="144"/>
+      <c r="AV5" s="144"/>
+      <c r="AW5" s="144"/>
+      <c r="AX5" s="144"/>
+      <c r="AY5" s="144"/>
+      <c r="AZ5" s="145"/>
+      <c r="BA5" s="143" t="s">
         <v>6</v>
       </c>
-      <c r="BB5" s="143"/>
-      <c r="BC5" s="143"/>
-      <c r="BD5" s="143"/>
-      <c r="BE5" s="143"/>
-      <c r="BF5" s="143"/>
-      <c r="BG5" s="143"/>
-      <c r="BH5" s="143"/>
-      <c r="BI5" s="143"/>
-      <c r="BJ5" s="143"/>
-      <c r="BK5" s="142" t="s">
+      <c r="BB5" s="144"/>
+      <c r="BC5" s="144"/>
+      <c r="BD5" s="144"/>
+      <c r="BE5" s="144"/>
+      <c r="BF5" s="144"/>
+      <c r="BG5" s="144"/>
+      <c r="BH5" s="144"/>
+      <c r="BI5" s="144"/>
+      <c r="BJ5" s="144"/>
+      <c r="BK5" s="143" t="s">
         <v>5</v>
       </c>
-      <c r="BL5" s="143"/>
-      <c r="BM5" s="144"/>
-      <c r="BN5" s="142" t="s">
+      <c r="BL5" s="144"/>
+      <c r="BM5" s="145"/>
+      <c r="BN5" s="143" t="s">
         <v>4</v>
       </c>
-      <c r="BO5" s="143"/>
-      <c r="BP5" s="143"/>
-      <c r="BQ5" s="144"/>
-      <c r="BR5" s="142" t="s">
+      <c r="BO5" s="144"/>
+      <c r="BP5" s="144"/>
+      <c r="BQ5" s="145"/>
+      <c r="BR5" s="143" t="s">
         <v>3</v>
       </c>
-      <c r="BS5" s="143"/>
-      <c r="BT5" s="143"/>
-      <c r="BU5" s="144"/>
+      <c r="BS5" s="144"/>
+      <c r="BT5" s="144"/>
+      <c r="BU5" s="145"/>
     </row>
     <row r="6" spans="1:73" s="22" customFormat="1" ht="15" customHeight="1">
-      <c r="A6" s="135"/>
-      <c r="B6" s="135"/>
-      <c r="C6" s="135"/>
-      <c r="D6" s="135"/>
-      <c r="E6" s="135"/>
-      <c r="F6" s="135"/>
-      <c r="G6" s="135" t="s">
+      <c r="A6" s="149"/>
+      <c r="B6" s="149"/>
+      <c r="C6" s="149"/>
+      <c r="D6" s="149"/>
+      <c r="E6" s="149"/>
+      <c r="F6" s="149"/>
+      <c r="G6" s="149" t="s">
         <v>2</v>
       </c>
-      <c r="H6" s="135"/>
-      <c r="I6" s="135"/>
-      <c r="J6" s="135"/>
-      <c r="K6" s="148" t="s">
+      <c r="H6" s="149"/>
+      <c r="I6" s="149"/>
+      <c r="J6" s="149"/>
+      <c r="K6" s="150" t="s">
         <v>22</v>
       </c>
-      <c r="L6" s="149"/>
-      <c r="M6" s="149"/>
-      <c r="N6" s="149"/>
-      <c r="O6" s="148" t="s">
+      <c r="L6" s="151"/>
+      <c r="M6" s="151"/>
+      <c r="N6" s="151"/>
+      <c r="O6" s="150" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="149"/>
-      <c r="Q6" s="149"/>
-      <c r="R6" s="149"/>
-      <c r="S6" s="149"/>
-      <c r="T6" s="150"/>
-      <c r="U6" s="140"/>
-      <c r="V6" s="140"/>
-      <c r="W6" s="140"/>
-      <c r="X6" s="140"/>
-      <c r="Y6" s="140"/>
-      <c r="Z6" s="141"/>
-      <c r="AA6" s="139"/>
-      <c r="AB6" s="140"/>
-      <c r="AC6" s="140"/>
-      <c r="AD6" s="140"/>
-      <c r="AE6" s="140"/>
-      <c r="AF6" s="140"/>
-      <c r="AG6" s="140"/>
-      <c r="AH6" s="140"/>
-      <c r="AI6" s="140"/>
-      <c r="AJ6" s="140"/>
-      <c r="AK6" s="140"/>
-      <c r="AL6" s="140"/>
-      <c r="AM6" s="140"/>
-      <c r="AN6" s="141"/>
-      <c r="AO6" s="145"/>
-      <c r="AP6" s="146"/>
-      <c r="AQ6" s="146"/>
-      <c r="AR6" s="146"/>
-      <c r="AS6" s="146"/>
-      <c r="AT6" s="146"/>
-      <c r="AU6" s="146"/>
-      <c r="AV6" s="146"/>
-      <c r="AW6" s="146"/>
-      <c r="AX6" s="146"/>
-      <c r="AY6" s="146"/>
-      <c r="AZ6" s="147"/>
-      <c r="BA6" s="145"/>
-      <c r="BB6" s="146"/>
-      <c r="BC6" s="146"/>
-      <c r="BD6" s="146"/>
-      <c r="BE6" s="146"/>
-      <c r="BF6" s="146"/>
-      <c r="BG6" s="146"/>
-      <c r="BH6" s="146"/>
-      <c r="BI6" s="146"/>
-      <c r="BJ6" s="146"/>
-      <c r="BK6" s="145"/>
-      <c r="BL6" s="146"/>
-      <c r="BM6" s="147"/>
-      <c r="BN6" s="145"/>
-      <c r="BO6" s="146"/>
-      <c r="BP6" s="146"/>
-      <c r="BQ6" s="147"/>
-      <c r="BR6" s="145"/>
-      <c r="BS6" s="146"/>
-      <c r="BT6" s="146"/>
-      <c r="BU6" s="147"/>
+      <c r="P6" s="151"/>
+      <c r="Q6" s="151"/>
+      <c r="R6" s="151"/>
+      <c r="S6" s="151"/>
+      <c r="T6" s="152"/>
+      <c r="U6" s="158"/>
+      <c r="V6" s="158"/>
+      <c r="W6" s="158"/>
+      <c r="X6" s="158"/>
+      <c r="Y6" s="158"/>
+      <c r="Z6" s="159"/>
+      <c r="AA6" s="157"/>
+      <c r="AB6" s="158"/>
+      <c r="AC6" s="158"/>
+      <c r="AD6" s="158"/>
+      <c r="AE6" s="158"/>
+      <c r="AF6" s="158"/>
+      <c r="AG6" s="158"/>
+      <c r="AH6" s="158"/>
+      <c r="AI6" s="158"/>
+      <c r="AJ6" s="158"/>
+      <c r="AK6" s="158"/>
+      <c r="AL6" s="158"/>
+      <c r="AM6" s="158"/>
+      <c r="AN6" s="159"/>
+      <c r="AO6" s="146"/>
+      <c r="AP6" s="147"/>
+      <c r="AQ6" s="147"/>
+      <c r="AR6" s="147"/>
+      <c r="AS6" s="147"/>
+      <c r="AT6" s="147"/>
+      <c r="AU6" s="147"/>
+      <c r="AV6" s="147"/>
+      <c r="AW6" s="147"/>
+      <c r="AX6" s="147"/>
+      <c r="AY6" s="147"/>
+      <c r="AZ6" s="148"/>
+      <c r="BA6" s="146"/>
+      <c r="BB6" s="147"/>
+      <c r="BC6" s="147"/>
+      <c r="BD6" s="147"/>
+      <c r="BE6" s="147"/>
+      <c r="BF6" s="147"/>
+      <c r="BG6" s="147"/>
+      <c r="BH6" s="147"/>
+      <c r="BI6" s="147"/>
+      <c r="BJ6" s="147"/>
+      <c r="BK6" s="146"/>
+      <c r="BL6" s="147"/>
+      <c r="BM6" s="148"/>
+      <c r="BN6" s="146"/>
+      <c r="BO6" s="147"/>
+      <c r="BP6" s="147"/>
+      <c r="BQ6" s="148"/>
+      <c r="BR6" s="146"/>
+      <c r="BS6" s="147"/>
+      <c r="BT6" s="147"/>
+      <c r="BU6" s="148"/>
     </row>
     <row r="7" spans="1:73" ht="15" customHeight="1">
       <c r="A7" s="28" t="s">
@@ -7539,18 +7530,18 @@
       <c r="BI7" s="18"/>
       <c r="BJ7" s="18"/>
       <c r="BK7" s="125" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="BL7" s="126"/>
       <c r="BM7" s="127"/>
-      <c r="BN7" s="151">
+      <c r="BN7" s="134">
         <v>45583</v>
       </c>
       <c r="BO7" s="126"/>
       <c r="BP7" s="126"/>
       <c r="BQ7" s="127"/>
       <c r="BR7" s="125" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="BS7" s="126"/>
       <c r="BT7" s="126"/>
@@ -7872,18 +7863,18 @@
       <c r="BI11" s="34"/>
       <c r="BJ11" s="34"/>
       <c r="BK11" s="125" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="BL11" s="126"/>
       <c r="BM11" s="127"/>
-      <c r="BN11" s="151">
+      <c r="BN11" s="134">
         <v>45583</v>
       </c>
       <c r="BO11" s="126"/>
       <c r="BP11" s="126"/>
       <c r="BQ11" s="127"/>
       <c r="BR11" s="125" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="BS11" s="126"/>
       <c r="BT11" s="126"/>
@@ -8205,18 +8196,18 @@
       <c r="BI15" s="34"/>
       <c r="BJ15" s="34"/>
       <c r="BK15" s="125" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="BL15" s="126"/>
       <c r="BM15" s="127"/>
-      <c r="BN15" s="151">
+      <c r="BN15" s="134">
         <v>45583</v>
       </c>
       <c r="BO15" s="126"/>
       <c r="BP15" s="126"/>
       <c r="BQ15" s="127"/>
       <c r="BR15" s="125" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="BS15" s="126"/>
       <c r="BT15" s="126"/>
@@ -8539,18 +8530,18 @@
       <c r="BI19" s="18"/>
       <c r="BJ19" s="18"/>
       <c r="BK19" s="125" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="BL19" s="126"/>
       <c r="BM19" s="127"/>
-      <c r="BN19" s="151">
+      <c r="BN19" s="134">
         <v>45583</v>
       </c>
       <c r="BO19" s="126"/>
       <c r="BP19" s="126"/>
       <c r="BQ19" s="127"/>
       <c r="BR19" s="125" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="BS19" s="126"/>
       <c r="BT19" s="126"/>
@@ -8873,18 +8864,18 @@
       <c r="BI23" s="18"/>
       <c r="BJ23" s="18"/>
       <c r="BK23" s="125" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="BL23" s="126"/>
       <c r="BM23" s="127"/>
-      <c r="BN23" s="151">
+      <c r="BN23" s="134">
         <v>45583</v>
       </c>
       <c r="BO23" s="126"/>
       <c r="BP23" s="126"/>
       <c r="BQ23" s="127"/>
       <c r="BR23" s="125" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="BS23" s="126"/>
       <c r="BT23" s="126"/>
@@ -9207,18 +9198,18 @@
       <c r="BI27" s="18"/>
       <c r="BJ27" s="18"/>
       <c r="BK27" s="125" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="BL27" s="126"/>
       <c r="BM27" s="127"/>
-      <c r="BN27" s="151">
+      <c r="BN27" s="134">
         <v>45583</v>
       </c>
       <c r="BO27" s="126"/>
       <c r="BP27" s="126"/>
       <c r="BQ27" s="127"/>
       <c r="BR27" s="125" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="BS27" s="126"/>
       <c r="BT27" s="126"/>
@@ -9541,18 +9532,18 @@
       <c r="BI31" s="18"/>
       <c r="BJ31" s="18"/>
       <c r="BK31" s="125" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="BL31" s="126"/>
       <c r="BM31" s="127"/>
-      <c r="BN31" s="151">
+      <c r="BN31" s="134">
         <v>45583</v>
       </c>
       <c r="BO31" s="126"/>
       <c r="BP31" s="126"/>
       <c r="BQ31" s="127"/>
       <c r="BR31" s="125" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="BS31" s="126"/>
       <c r="BT31" s="126"/>
@@ -9875,18 +9866,18 @@
       <c r="BI35" s="25"/>
       <c r="BJ35" s="25"/>
       <c r="BK35" s="125" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="BL35" s="126"/>
       <c r="BM35" s="127"/>
-      <c r="BN35" s="151">
+      <c r="BN35" s="134">
         <v>45583</v>
       </c>
-      <c r="BO35" s="152"/>
-      <c r="BP35" s="152"/>
-      <c r="BQ35" s="153"/>
+      <c r="BO35" s="135"/>
+      <c r="BP35" s="135"/>
+      <c r="BQ35" s="136"/>
       <c r="BR35" s="125" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="BS35" s="126"/>
       <c r="BT35" s="126"/>
@@ -9964,10 +9955,10 @@
       <c r="BK36" s="128"/>
       <c r="BL36" s="129"/>
       <c r="BM36" s="130"/>
-      <c r="BN36" s="154"/>
-      <c r="BO36" s="155"/>
-      <c r="BP36" s="155"/>
-      <c r="BQ36" s="156"/>
+      <c r="BN36" s="137"/>
+      <c r="BO36" s="138"/>
+      <c r="BP36" s="138"/>
+      <c r="BQ36" s="139"/>
       <c r="BR36" s="128"/>
       <c r="BS36" s="129"/>
       <c r="BT36" s="129"/>
@@ -10045,10 +10036,10 @@
       <c r="BK37" s="128"/>
       <c r="BL37" s="129"/>
       <c r="BM37" s="130"/>
-      <c r="BN37" s="154"/>
-      <c r="BO37" s="155"/>
-      <c r="BP37" s="155"/>
-      <c r="BQ37" s="156"/>
+      <c r="BN37" s="137"/>
+      <c r="BO37" s="138"/>
+      <c r="BP37" s="138"/>
+      <c r="BQ37" s="139"/>
       <c r="BR37" s="128"/>
       <c r="BS37" s="129"/>
       <c r="BT37" s="129"/>
@@ -10124,10 +10115,10 @@
       <c r="BK38" s="128"/>
       <c r="BL38" s="129"/>
       <c r="BM38" s="130"/>
-      <c r="BN38" s="154"/>
-      <c r="BO38" s="155"/>
-      <c r="BP38" s="155"/>
-      <c r="BQ38" s="156"/>
+      <c r="BN38" s="137"/>
+      <c r="BO38" s="138"/>
+      <c r="BP38" s="138"/>
+      <c r="BQ38" s="139"/>
       <c r="BR38" s="128"/>
       <c r="BS38" s="129"/>
       <c r="BT38" s="129"/>
@@ -10201,10 +10192,10 @@
       <c r="BK39" s="128"/>
       <c r="BL39" s="129"/>
       <c r="BM39" s="130"/>
-      <c r="BN39" s="154"/>
-      <c r="BO39" s="155"/>
-      <c r="BP39" s="155"/>
-      <c r="BQ39" s="156"/>
+      <c r="BN39" s="137"/>
+      <c r="BO39" s="138"/>
+      <c r="BP39" s="138"/>
+      <c r="BQ39" s="139"/>
       <c r="BR39" s="128"/>
       <c r="BS39" s="129"/>
       <c r="BT39" s="129"/>
@@ -10278,10 +10269,10 @@
       <c r="BK40" s="128"/>
       <c r="BL40" s="129"/>
       <c r="BM40" s="130"/>
-      <c r="BN40" s="154"/>
-      <c r="BO40" s="155"/>
-      <c r="BP40" s="155"/>
-      <c r="BQ40" s="156"/>
+      <c r="BN40" s="137"/>
+      <c r="BO40" s="138"/>
+      <c r="BP40" s="138"/>
+      <c r="BQ40" s="139"/>
       <c r="BR40" s="128"/>
       <c r="BS40" s="129"/>
       <c r="BT40" s="129"/>
@@ -10355,10 +10346,10 @@
       <c r="BK41" s="128"/>
       <c r="BL41" s="129"/>
       <c r="BM41" s="130"/>
-      <c r="BN41" s="154"/>
-      <c r="BO41" s="155"/>
-      <c r="BP41" s="155"/>
-      <c r="BQ41" s="156"/>
+      <c r="BN41" s="137"/>
+      <c r="BO41" s="138"/>
+      <c r="BP41" s="138"/>
+      <c r="BQ41" s="139"/>
       <c r="BR41" s="128"/>
       <c r="BS41" s="129"/>
       <c r="BT41" s="129"/>
@@ -10432,10 +10423,10 @@
       <c r="BK42" s="128"/>
       <c r="BL42" s="129"/>
       <c r="BM42" s="130"/>
-      <c r="BN42" s="154"/>
-      <c r="BO42" s="155"/>
-      <c r="BP42" s="155"/>
-      <c r="BQ42" s="156"/>
+      <c r="BN42" s="137"/>
+      <c r="BO42" s="138"/>
+      <c r="BP42" s="138"/>
+      <c r="BQ42" s="139"/>
       <c r="BR42" s="128"/>
       <c r="BS42" s="129"/>
       <c r="BT42" s="129"/>
@@ -10509,10 +10500,10 @@
       <c r="BK43" s="131"/>
       <c r="BL43" s="132"/>
       <c r="BM43" s="133"/>
-      <c r="BN43" s="157"/>
-      <c r="BO43" s="158"/>
-      <c r="BP43" s="158"/>
-      <c r="BQ43" s="159"/>
+      <c r="BN43" s="140"/>
+      <c r="BO43" s="141"/>
+      <c r="BP43" s="141"/>
+      <c r="BQ43" s="142"/>
       <c r="BR43" s="131"/>
       <c r="BS43" s="132"/>
       <c r="BT43" s="132"/>
@@ -10558,7 +10549,7 @@
       <c r="Y44" s="25"/>
       <c r="Z44" s="25"/>
       <c r="AA44" s="14" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="AB44" s="12"/>
       <c r="AC44" s="13"/>
@@ -10600,11 +10591,11 @@
       <c r="BI44" s="12"/>
       <c r="BJ44" s="12"/>
       <c r="BK44" s="125" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="BL44" s="126"/>
       <c r="BM44" s="127"/>
-      <c r="BN44" s="151">
+      <c r="BN44" s="134">
         <v>45583</v>
       </c>
       <c r="BO44" s="126"/>
@@ -10633,7 +10624,7 @@
       <c r="M45" s="25"/>
       <c r="N45" s="25"/>
       <c r="O45" s="14" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="P45" s="25"/>
       <c r="Q45" s="25"/>
@@ -10647,7 +10638,7 @@
       <c r="Y45" s="25"/>
       <c r="Z45" s="25"/>
       <c r="AA45" s="14" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="AB45" s="12"/>
       <c r="AC45" s="13"/>
@@ -10663,7 +10654,7 @@
       <c r="AM45" s="12"/>
       <c r="AN45" s="10"/>
       <c r="AO45" s="11" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="AP45" s="10"/>
       <c r="AQ45" s="10"/>
@@ -10726,7 +10717,7 @@
       <c r="Y46" s="25"/>
       <c r="Z46" s="25"/>
       <c r="AA46" s="14" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="AB46" s="12"/>
       <c r="AC46" s="13"/>
@@ -10803,7 +10794,7 @@
       <c r="Y47" s="5"/>
       <c r="Z47" s="5"/>
       <c r="AA47" s="7" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="AB47" s="5"/>
       <c r="AC47" s="6"/>
@@ -10892,7 +10883,7 @@
       <c r="Y48" s="25"/>
       <c r="Z48" s="25"/>
       <c r="AA48" s="14" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="AB48" s="12"/>
       <c r="AC48" s="13"/>
@@ -10934,11 +10925,11 @@
       <c r="BI48" s="12"/>
       <c r="BJ48" s="12"/>
       <c r="BK48" s="125" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="BL48" s="126"/>
       <c r="BM48" s="127"/>
-      <c r="BN48" s="151">
+      <c r="BN48" s="134">
         <v>45583</v>
       </c>
       <c r="BO48" s="126"/>
@@ -10967,7 +10958,7 @@
       <c r="M49" s="25"/>
       <c r="N49" s="25"/>
       <c r="O49" s="14" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="P49" s="25"/>
       <c r="Q49" s="25"/>
@@ -10981,7 +10972,7 @@
       <c r="Y49" s="25"/>
       <c r="Z49" s="25"/>
       <c r="AA49" s="14" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="AB49" s="12"/>
       <c r="AC49" s="13"/>
@@ -10997,7 +10988,7 @@
       <c r="AM49" s="12"/>
       <c r="AN49" s="10"/>
       <c r="AO49" s="11" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="AP49" s="10"/>
       <c r="AQ49" s="10"/>
@@ -11060,7 +11051,7 @@
       <c r="Y50" s="25"/>
       <c r="Z50" s="25"/>
       <c r="AA50" s="14" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="AB50" s="12"/>
       <c r="AC50" s="13"/>
@@ -11137,7 +11128,7 @@
       <c r="Y51" s="5"/>
       <c r="Z51" s="5"/>
       <c r="AA51" s="7" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="AB51" s="5"/>
       <c r="AC51" s="6"/>
@@ -11268,18 +11259,18 @@
       <c r="BI52" s="18"/>
       <c r="BJ52" s="18"/>
       <c r="BK52" s="125" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="BL52" s="126"/>
       <c r="BM52" s="127"/>
-      <c r="BN52" s="151">
+      <c r="BN52" s="134">
         <v>45583</v>
       </c>
-      <c r="BO52" s="152"/>
-      <c r="BP52" s="152"/>
-      <c r="BQ52" s="153"/>
+      <c r="BO52" s="135"/>
+      <c r="BP52" s="135"/>
+      <c r="BQ52" s="136"/>
       <c r="BR52" s="125" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="BS52" s="126"/>
       <c r="BT52" s="126"/>
@@ -11355,10 +11346,10 @@
       <c r="BK53" s="128"/>
       <c r="BL53" s="129"/>
       <c r="BM53" s="130"/>
-      <c r="BN53" s="154"/>
-      <c r="BO53" s="155"/>
-      <c r="BP53" s="155"/>
-      <c r="BQ53" s="156"/>
+      <c r="BN53" s="137"/>
+      <c r="BO53" s="138"/>
+      <c r="BP53" s="138"/>
+      <c r="BQ53" s="139"/>
       <c r="BR53" s="128"/>
       <c r="BS53" s="129"/>
       <c r="BT53" s="129"/>
@@ -11432,10 +11423,10 @@
       <c r="BK54" s="128"/>
       <c r="BL54" s="129"/>
       <c r="BM54" s="130"/>
-      <c r="BN54" s="154"/>
-      <c r="BO54" s="155"/>
-      <c r="BP54" s="155"/>
-      <c r="BQ54" s="156"/>
+      <c r="BN54" s="137"/>
+      <c r="BO54" s="138"/>
+      <c r="BP54" s="138"/>
+      <c r="BQ54" s="139"/>
       <c r="BR54" s="128"/>
       <c r="BS54" s="129"/>
       <c r="BT54" s="129"/>
@@ -11511,10 +11502,10 @@
       <c r="BK55" s="131"/>
       <c r="BL55" s="132"/>
       <c r="BM55" s="133"/>
-      <c r="BN55" s="157"/>
-      <c r="BO55" s="158"/>
-      <c r="BP55" s="158"/>
-      <c r="BQ55" s="159"/>
+      <c r="BN55" s="140"/>
+      <c r="BO55" s="141"/>
+      <c r="BP55" s="141"/>
+      <c r="BQ55" s="142"/>
       <c r="BR55" s="131"/>
       <c r="BS55" s="132"/>
       <c r="BT55" s="132"/>
@@ -11602,18 +11593,18 @@
       <c r="BI56" s="12"/>
       <c r="BJ56" s="12"/>
       <c r="BK56" s="125" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="BL56" s="126"/>
       <c r="BM56" s="127"/>
-      <c r="BN56" s="151">
+      <c r="BN56" s="134">
         <v>45583</v>
       </c>
-      <c r="BO56" s="152"/>
-      <c r="BP56" s="152"/>
-      <c r="BQ56" s="153"/>
+      <c r="BO56" s="135"/>
+      <c r="BP56" s="135"/>
+      <c r="BQ56" s="136"/>
       <c r="BR56" s="125" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="BS56" s="126"/>
       <c r="BT56" s="126"/>
@@ -11691,10 +11682,10 @@
       <c r="BK57" s="128"/>
       <c r="BL57" s="129"/>
       <c r="BM57" s="130"/>
-      <c r="BN57" s="154"/>
-      <c r="BO57" s="155"/>
-      <c r="BP57" s="155"/>
-      <c r="BQ57" s="156"/>
+      <c r="BN57" s="137"/>
+      <c r="BO57" s="138"/>
+      <c r="BP57" s="138"/>
+      <c r="BQ57" s="139"/>
       <c r="BR57" s="128"/>
       <c r="BS57" s="129"/>
       <c r="BT57" s="129"/>
@@ -11768,10 +11759,10 @@
       <c r="BK58" s="128"/>
       <c r="BL58" s="129"/>
       <c r="BM58" s="130"/>
-      <c r="BN58" s="154"/>
-      <c r="BO58" s="155"/>
-      <c r="BP58" s="155"/>
-      <c r="BQ58" s="156"/>
+      <c r="BN58" s="137"/>
+      <c r="BO58" s="138"/>
+      <c r="BP58" s="138"/>
+      <c r="BQ58" s="139"/>
       <c r="BR58" s="128"/>
       <c r="BS58" s="129"/>
       <c r="BT58" s="129"/>
@@ -11845,10 +11836,10 @@
       <c r="BK59" s="131"/>
       <c r="BL59" s="132"/>
       <c r="BM59" s="133"/>
-      <c r="BN59" s="157"/>
-      <c r="BO59" s="158"/>
-      <c r="BP59" s="158"/>
-      <c r="BQ59" s="159"/>
+      <c r="BN59" s="140"/>
+      <c r="BO59" s="141"/>
+      <c r="BP59" s="141"/>
+      <c r="BQ59" s="142"/>
       <c r="BR59" s="131"/>
       <c r="BS59" s="132"/>
       <c r="BT59" s="132"/>
@@ -11936,18 +11927,18 @@
       <c r="BI60" s="12"/>
       <c r="BJ60" s="12"/>
       <c r="BK60" s="125" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="BL60" s="126"/>
       <c r="BM60" s="127"/>
-      <c r="BN60" s="151">
+      <c r="BN60" s="134">
         <v>45583</v>
       </c>
-      <c r="BO60" s="152"/>
-      <c r="BP60" s="152"/>
-      <c r="BQ60" s="153"/>
+      <c r="BO60" s="135"/>
+      <c r="BP60" s="135"/>
+      <c r="BQ60" s="136"/>
       <c r="BR60" s="125" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="BS60" s="126"/>
       <c r="BT60" s="126"/>
@@ -12025,10 +12016,10 @@
       <c r="BK61" s="128"/>
       <c r="BL61" s="129"/>
       <c r="BM61" s="130"/>
-      <c r="BN61" s="154"/>
-      <c r="BO61" s="155"/>
-      <c r="BP61" s="155"/>
-      <c r="BQ61" s="156"/>
+      <c r="BN61" s="137"/>
+      <c r="BO61" s="138"/>
+      <c r="BP61" s="138"/>
+      <c r="BQ61" s="139"/>
       <c r="BR61" s="128"/>
       <c r="BS61" s="129"/>
       <c r="BT61" s="129"/>
@@ -12102,10 +12093,10 @@
       <c r="BK62" s="128"/>
       <c r="BL62" s="129"/>
       <c r="BM62" s="130"/>
-      <c r="BN62" s="154"/>
-      <c r="BO62" s="155"/>
-      <c r="BP62" s="155"/>
-      <c r="BQ62" s="156"/>
+      <c r="BN62" s="137"/>
+      <c r="BO62" s="138"/>
+      <c r="BP62" s="138"/>
+      <c r="BQ62" s="139"/>
       <c r="BR62" s="128"/>
       <c r="BS62" s="129"/>
       <c r="BT62" s="129"/>
@@ -12179,10 +12170,10 @@
       <c r="BK63" s="131"/>
       <c r="BL63" s="132"/>
       <c r="BM63" s="133"/>
-      <c r="BN63" s="157"/>
-      <c r="BO63" s="158"/>
-      <c r="BP63" s="158"/>
-      <c r="BQ63" s="159"/>
+      <c r="BN63" s="140"/>
+      <c r="BO63" s="141"/>
+      <c r="BP63" s="141"/>
+      <c r="BQ63" s="142"/>
       <c r="BR63" s="131"/>
       <c r="BS63" s="132"/>
       <c r="BT63" s="132"/>
@@ -12270,16 +12261,16 @@
       <c r="BI64" s="12"/>
       <c r="BJ64" s="12"/>
       <c r="BK64" s="125" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="BL64" s="126"/>
       <c r="BM64" s="127"/>
-      <c r="BN64" s="151">
+      <c r="BN64" s="134">
         <v>45583</v>
       </c>
-      <c r="BO64" s="152"/>
-      <c r="BP64" s="152"/>
-      <c r="BQ64" s="153"/>
+      <c r="BO64" s="135"/>
+      <c r="BP64" s="135"/>
+      <c r="BQ64" s="136"/>
       <c r="BR64" s="125" t="s">
         <v>28</v>
       </c>
@@ -12333,7 +12324,7 @@
       <c r="AM65" s="12"/>
       <c r="AN65" s="10"/>
       <c r="AO65" s="11" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="AP65" s="10"/>
       <c r="AQ65" s="10"/>
@@ -12359,10 +12350,10 @@
       <c r="BK65" s="128"/>
       <c r="BL65" s="129"/>
       <c r="BM65" s="130"/>
-      <c r="BN65" s="154"/>
-      <c r="BO65" s="155"/>
-      <c r="BP65" s="155"/>
-      <c r="BQ65" s="156"/>
+      <c r="BN65" s="137"/>
+      <c r="BO65" s="138"/>
+      <c r="BP65" s="138"/>
+      <c r="BQ65" s="139"/>
       <c r="BR65" s="128"/>
       <c r="BS65" s="129"/>
       <c r="BT65" s="129"/>
@@ -12436,10 +12427,10 @@
       <c r="BK66" s="128"/>
       <c r="BL66" s="129"/>
       <c r="BM66" s="130"/>
-      <c r="BN66" s="154"/>
-      <c r="BO66" s="155"/>
-      <c r="BP66" s="155"/>
-      <c r="BQ66" s="156"/>
+      <c r="BN66" s="137"/>
+      <c r="BO66" s="138"/>
+      <c r="BP66" s="138"/>
+      <c r="BQ66" s="139"/>
       <c r="BR66" s="128"/>
       <c r="BS66" s="129"/>
       <c r="BT66" s="129"/>
@@ -12513,10 +12504,10 @@
       <c r="BK67" s="131"/>
       <c r="BL67" s="132"/>
       <c r="BM67" s="133"/>
-      <c r="BN67" s="157"/>
-      <c r="BO67" s="158"/>
-      <c r="BP67" s="158"/>
-      <c r="BQ67" s="159"/>
+      <c r="BN67" s="140"/>
+      <c r="BO67" s="141"/>
+      <c r="BP67" s="141"/>
+      <c r="BQ67" s="142"/>
       <c r="BR67" s="131"/>
       <c r="BS67" s="132"/>
       <c r="BT67" s="132"/>
@@ -12604,16 +12595,16 @@
       <c r="BI68" s="12"/>
       <c r="BJ68" s="12"/>
       <c r="BK68" s="125" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="BL68" s="126"/>
       <c r="BM68" s="127"/>
-      <c r="BN68" s="151">
+      <c r="BN68" s="134">
         <v>45583</v>
       </c>
-      <c r="BO68" s="152"/>
-      <c r="BP68" s="152"/>
-      <c r="BQ68" s="153"/>
+      <c r="BO68" s="135"/>
+      <c r="BP68" s="135"/>
+      <c r="BQ68" s="136"/>
       <c r="BR68" s="125" t="s">
         <v>28</v>
       </c>
@@ -12692,10 +12683,10 @@
       <c r="BK69" s="128"/>
       <c r="BL69" s="129"/>
       <c r="BM69" s="130"/>
-      <c r="BN69" s="154"/>
-      <c r="BO69" s="155"/>
-      <c r="BP69" s="155"/>
-      <c r="BQ69" s="156"/>
+      <c r="BN69" s="137"/>
+      <c r="BO69" s="138"/>
+      <c r="BP69" s="138"/>
+      <c r="BQ69" s="139"/>
       <c r="BR69" s="128"/>
       <c r="BS69" s="129"/>
       <c r="BT69" s="129"/>
@@ -12768,10 +12759,10 @@
       <c r="BK70" s="128"/>
       <c r="BL70" s="129"/>
       <c r="BM70" s="130"/>
-      <c r="BN70" s="154"/>
-      <c r="BO70" s="155"/>
-      <c r="BP70" s="155"/>
-      <c r="BQ70" s="156"/>
+      <c r="BN70" s="137"/>
+      <c r="BO70" s="138"/>
+      <c r="BP70" s="138"/>
+      <c r="BQ70" s="139"/>
       <c r="BR70" s="128"/>
       <c r="BS70" s="129"/>
       <c r="BT70" s="129"/>
@@ -12845,10 +12836,10 @@
       <c r="BK71" s="131"/>
       <c r="BL71" s="132"/>
       <c r="BM71" s="133"/>
-      <c r="BN71" s="157"/>
-      <c r="BO71" s="158"/>
-      <c r="BP71" s="158"/>
-      <c r="BQ71" s="159"/>
+      <c r="BN71" s="140"/>
+      <c r="BO71" s="141"/>
+      <c r="BP71" s="141"/>
+      <c r="BQ71" s="142"/>
       <c r="BR71" s="131"/>
       <c r="BS71" s="132"/>
       <c r="BT71" s="132"/>
@@ -12936,16 +12927,16 @@
       <c r="BI72" s="12"/>
       <c r="BJ72" s="12"/>
       <c r="BK72" s="125" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="BL72" s="126"/>
       <c r="BM72" s="127"/>
-      <c r="BN72" s="151">
+      <c r="BN72" s="134">
         <v>45583</v>
       </c>
-      <c r="BO72" s="152"/>
-      <c r="BP72" s="152"/>
-      <c r="BQ72" s="153"/>
+      <c r="BO72" s="135"/>
+      <c r="BP72" s="135"/>
+      <c r="BQ72" s="136"/>
       <c r="BR72" s="125" t="s">
         <v>28</v>
       </c>
@@ -13024,10 +13015,10 @@
       <c r="BK73" s="128"/>
       <c r="BL73" s="129"/>
       <c r="BM73" s="130"/>
-      <c r="BN73" s="154"/>
-      <c r="BO73" s="155"/>
-      <c r="BP73" s="155"/>
-      <c r="BQ73" s="156"/>
+      <c r="BN73" s="137"/>
+      <c r="BO73" s="138"/>
+      <c r="BP73" s="138"/>
+      <c r="BQ73" s="139"/>
       <c r="BR73" s="128"/>
       <c r="BS73" s="129"/>
       <c r="BT73" s="129"/>
@@ -13100,10 +13091,10 @@
       <c r="BK74" s="128"/>
       <c r="BL74" s="129"/>
       <c r="BM74" s="130"/>
-      <c r="BN74" s="154"/>
-      <c r="BO74" s="155"/>
-      <c r="BP74" s="155"/>
-      <c r="BQ74" s="156"/>
+      <c r="BN74" s="137"/>
+      <c r="BO74" s="138"/>
+      <c r="BP74" s="138"/>
+      <c r="BQ74" s="139"/>
       <c r="BR74" s="128"/>
       <c r="BS74" s="129"/>
       <c r="BT74" s="129"/>
@@ -13177,10 +13168,10 @@
       <c r="BK75" s="131"/>
       <c r="BL75" s="132"/>
       <c r="BM75" s="133"/>
-      <c r="BN75" s="157"/>
-      <c r="BO75" s="158"/>
-      <c r="BP75" s="158"/>
-      <c r="BQ75" s="159"/>
+      <c r="BN75" s="140"/>
+      <c r="BO75" s="141"/>
+      <c r="BP75" s="141"/>
+      <c r="BQ75" s="142"/>
       <c r="BR75" s="131"/>
       <c r="BS75" s="132"/>
       <c r="BT75" s="132"/>
@@ -13268,16 +13259,16 @@
       <c r="BI76" s="12"/>
       <c r="BJ76" s="12"/>
       <c r="BK76" s="125" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="BL76" s="126"/>
       <c r="BM76" s="127"/>
-      <c r="BN76" s="151">
+      <c r="BN76" s="134">
         <v>45583</v>
       </c>
-      <c r="BO76" s="152"/>
-      <c r="BP76" s="152"/>
-      <c r="BQ76" s="153"/>
+      <c r="BO76" s="135"/>
+      <c r="BP76" s="135"/>
+      <c r="BQ76" s="136"/>
       <c r="BR76" s="125" t="s">
         <v>28</v>
       </c>
@@ -13356,10 +13347,10 @@
       <c r="BK77" s="128"/>
       <c r="BL77" s="129"/>
       <c r="BM77" s="130"/>
-      <c r="BN77" s="154"/>
-      <c r="BO77" s="155"/>
-      <c r="BP77" s="155"/>
-      <c r="BQ77" s="156"/>
+      <c r="BN77" s="137"/>
+      <c r="BO77" s="138"/>
+      <c r="BP77" s="138"/>
+      <c r="BQ77" s="139"/>
       <c r="BR77" s="128"/>
       <c r="BS77" s="129"/>
       <c r="BT77" s="129"/>
@@ -13432,10 +13423,10 @@
       <c r="BK78" s="128"/>
       <c r="BL78" s="129"/>
       <c r="BM78" s="130"/>
-      <c r="BN78" s="154"/>
-      <c r="BO78" s="155"/>
-      <c r="BP78" s="155"/>
-      <c r="BQ78" s="156"/>
+      <c r="BN78" s="137"/>
+      <c r="BO78" s="138"/>
+      <c r="BP78" s="138"/>
+      <c r="BQ78" s="139"/>
       <c r="BR78" s="128"/>
       <c r="BS78" s="129"/>
       <c r="BT78" s="129"/>
@@ -13509,10 +13500,10 @@
       <c r="BK79" s="131"/>
       <c r="BL79" s="132"/>
       <c r="BM79" s="133"/>
-      <c r="BN79" s="157"/>
-      <c r="BO79" s="158"/>
-      <c r="BP79" s="158"/>
-      <c r="BQ79" s="159"/>
+      <c r="BN79" s="140"/>
+      <c r="BO79" s="141"/>
+      <c r="BP79" s="141"/>
+      <c r="BQ79" s="142"/>
       <c r="BR79" s="131"/>
       <c r="BS79" s="132"/>
       <c r="BT79" s="132"/>
@@ -13600,16 +13591,16 @@
       <c r="BI80" s="12"/>
       <c r="BJ80" s="12"/>
       <c r="BK80" s="125" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="BL80" s="126"/>
       <c r="BM80" s="127"/>
-      <c r="BN80" s="151">
+      <c r="BN80" s="134">
         <v>45583</v>
       </c>
-      <c r="BO80" s="152"/>
-      <c r="BP80" s="152"/>
-      <c r="BQ80" s="153"/>
+      <c r="BO80" s="135"/>
+      <c r="BP80" s="135"/>
+      <c r="BQ80" s="136"/>
       <c r="BR80" s="125" t="s">
         <v>28</v>
       </c>
@@ -13688,10 +13679,10 @@
       <c r="BK81" s="128"/>
       <c r="BL81" s="129"/>
       <c r="BM81" s="130"/>
-      <c r="BN81" s="154"/>
-      <c r="BO81" s="155"/>
-      <c r="BP81" s="155"/>
-      <c r="BQ81" s="156"/>
+      <c r="BN81" s="137"/>
+      <c r="BO81" s="138"/>
+      <c r="BP81" s="138"/>
+      <c r="BQ81" s="139"/>
       <c r="BR81" s="128"/>
       <c r="BS81" s="129"/>
       <c r="BT81" s="129"/>
@@ -13765,10 +13756,10 @@
       <c r="BK82" s="128"/>
       <c r="BL82" s="129"/>
       <c r="BM82" s="130"/>
-      <c r="BN82" s="154"/>
-      <c r="BO82" s="155"/>
-      <c r="BP82" s="155"/>
-      <c r="BQ82" s="156"/>
+      <c r="BN82" s="137"/>
+      <c r="BO82" s="138"/>
+      <c r="BP82" s="138"/>
+      <c r="BQ82" s="139"/>
       <c r="BR82" s="128"/>
       <c r="BS82" s="129"/>
       <c r="BT82" s="129"/>
@@ -13842,10 +13833,10 @@
       <c r="BK83" s="131"/>
       <c r="BL83" s="132"/>
       <c r="BM83" s="133"/>
-      <c r="BN83" s="157"/>
-      <c r="BO83" s="158"/>
-      <c r="BP83" s="158"/>
-      <c r="BQ83" s="159"/>
+      <c r="BN83" s="140"/>
+      <c r="BO83" s="141"/>
+      <c r="BP83" s="141"/>
+      <c r="BQ83" s="142"/>
       <c r="BR83" s="131"/>
       <c r="BS83" s="132"/>
       <c r="BT83" s="132"/>
@@ -13933,16 +13924,16 @@
       <c r="BI84" s="12"/>
       <c r="BJ84" s="12"/>
       <c r="BK84" s="125" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="BL84" s="126"/>
       <c r="BM84" s="127"/>
-      <c r="BN84" s="151">
+      <c r="BN84" s="134">
         <v>45583</v>
       </c>
-      <c r="BO84" s="152"/>
-      <c r="BP84" s="152"/>
-      <c r="BQ84" s="153"/>
+      <c r="BO84" s="135"/>
+      <c r="BP84" s="135"/>
+      <c r="BQ84" s="136"/>
       <c r="BR84" s="125" t="s">
         <v>28</v>
       </c>
@@ -14022,10 +14013,10 @@
       <c r="BK85" s="128"/>
       <c r="BL85" s="129"/>
       <c r="BM85" s="130"/>
-      <c r="BN85" s="154"/>
-      <c r="BO85" s="155"/>
-      <c r="BP85" s="155"/>
-      <c r="BQ85" s="156"/>
+      <c r="BN85" s="137"/>
+      <c r="BO85" s="138"/>
+      <c r="BP85" s="138"/>
+      <c r="BQ85" s="139"/>
       <c r="BR85" s="128"/>
       <c r="BS85" s="129"/>
       <c r="BT85" s="129"/>
@@ -14099,10 +14090,10 @@
       <c r="BK86" s="128"/>
       <c r="BL86" s="129"/>
       <c r="BM86" s="130"/>
-      <c r="BN86" s="154"/>
-      <c r="BO86" s="155"/>
-      <c r="BP86" s="155"/>
-      <c r="BQ86" s="156"/>
+      <c r="BN86" s="137"/>
+      <c r="BO86" s="138"/>
+      <c r="BP86" s="138"/>
+      <c r="BQ86" s="139"/>
       <c r="BR86" s="128"/>
       <c r="BS86" s="129"/>
       <c r="BT86" s="129"/>
@@ -14176,10 +14167,10 @@
       <c r="BK87" s="131"/>
       <c r="BL87" s="132"/>
       <c r="BM87" s="133"/>
-      <c r="BN87" s="157"/>
-      <c r="BO87" s="158"/>
-      <c r="BP87" s="158"/>
-      <c r="BQ87" s="159"/>
+      <c r="BN87" s="140"/>
+      <c r="BO87" s="141"/>
+      <c r="BP87" s="141"/>
+      <c r="BQ87" s="142"/>
       <c r="BR87" s="131"/>
       <c r="BS87" s="132"/>
       <c r="BT87" s="132"/>
@@ -14255,7 +14246,7 @@
       <c r="AY88" s="12"/>
       <c r="AZ88" s="12"/>
       <c r="BA88" s="11" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="BB88" s="10"/>
       <c r="BC88" s="10"/>
@@ -14267,11 +14258,11 @@
       <c r="BI88" s="12"/>
       <c r="BJ88" s="12"/>
       <c r="BK88" s="125" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="BL88" s="126"/>
       <c r="BM88" s="127"/>
-      <c r="BN88" s="151">
+      <c r="BN88" s="134">
         <v>45583</v>
       </c>
       <c r="BO88" s="126"/>
@@ -14312,7 +14303,7 @@
       <c r="Y89" s="12"/>
       <c r="Z89" s="12"/>
       <c r="AA89" s="14" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="AB89" s="12"/>
       <c r="AC89" s="13"/>
@@ -14342,7 +14333,7 @@
       <c r="AY89" s="12"/>
       <c r="AZ89" s="12"/>
       <c r="BA89" s="11" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="BB89" s="10"/>
       <c r="BC89" s="10"/>
@@ -14418,9 +14409,7 @@
       <c r="AX90" s="12"/>
       <c r="AY90" s="12"/>
       <c r="AZ90" s="12"/>
-      <c r="BA90" s="11" t="s">
-        <v>174</v>
-      </c>
+      <c r="BA90" s="11"/>
       <c r="BB90" s="10"/>
       <c r="BC90" s="10"/>
       <c r="BD90" s="10"/>
@@ -14495,9 +14484,7 @@
       <c r="AX91" s="5"/>
       <c r="AY91" s="5"/>
       <c r="AZ91" s="5"/>
-      <c r="BA91" s="4" t="s">
-        <v>188</v>
-      </c>
+      <c r="BA91" s="4"/>
       <c r="BB91" s="3"/>
       <c r="BC91" s="3"/>
       <c r="BD91" s="3"/>
@@ -14589,7 +14576,7 @@
       <c r="AY92" s="12"/>
       <c r="AZ92" s="12"/>
       <c r="BA92" s="11" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="BB92" s="10"/>
       <c r="BC92" s="10"/>
@@ -14600,14 +14587,20 @@
       <c r="BH92" s="10"/>
       <c r="BI92" s="12"/>
       <c r="BJ92" s="12"/>
-      <c r="BK92" s="125"/>
+      <c r="BK92" s="125" t="s">
+        <v>185</v>
+      </c>
       <c r="BL92" s="126"/>
       <c r="BM92" s="127"/>
-      <c r="BN92" s="125"/>
+      <c r="BN92" s="134">
+        <v>45586</v>
+      </c>
       <c r="BO92" s="126"/>
       <c r="BP92" s="126"/>
       <c r="BQ92" s="127"/>
-      <c r="BR92" s="125"/>
+      <c r="BR92" s="125" t="s">
+        <v>28</v>
+      </c>
       <c r="BS92" s="126"/>
       <c r="BT92" s="126"/>
       <c r="BU92" s="127"/>
@@ -14640,7 +14633,7 @@
       <c r="Y93" s="12"/>
       <c r="Z93" s="12"/>
       <c r="AA93" s="14" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="AB93" s="12"/>
       <c r="AC93" s="13"/>
@@ -14670,7 +14663,7 @@
       <c r="AY93" s="12"/>
       <c r="AZ93" s="12"/>
       <c r="BA93" s="11" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="BB93" s="10"/>
       <c r="BC93" s="10"/>
@@ -14746,9 +14739,7 @@
       <c r="AX94" s="12"/>
       <c r="AY94" s="12"/>
       <c r="AZ94" s="12"/>
-      <c r="BA94" s="11" t="s">
-        <v>174</v>
-      </c>
+      <c r="BA94" s="11"/>
       <c r="BB94" s="10"/>
       <c r="BC94" s="10"/>
       <c r="BD94" s="10"/>
@@ -14823,9 +14814,7 @@
       <c r="AX95" s="5"/>
       <c r="AY95" s="5"/>
       <c r="AZ95" s="5"/>
-      <c r="BA95" s="4" t="s">
-        <v>188</v>
-      </c>
+      <c r="BA95" s="4"/>
       <c r="BB95" s="3"/>
       <c r="BC95" s="3"/>
       <c r="BD95" s="3"/>
@@ -14917,7 +14906,7 @@
       <c r="AY96" s="12"/>
       <c r="AZ96" s="12"/>
       <c r="BA96" s="11" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="BB96" s="10"/>
       <c r="BC96" s="10"/>
@@ -14928,14 +14917,20 @@
       <c r="BH96" s="10"/>
       <c r="BI96" s="12"/>
       <c r="BJ96" s="12"/>
-      <c r="BK96" s="125"/>
+      <c r="BK96" s="125" t="s">
+        <v>185</v>
+      </c>
       <c r="BL96" s="126"/>
       <c r="BM96" s="127"/>
-      <c r="BN96" s="125"/>
+      <c r="BN96" s="134">
+        <v>45586</v>
+      </c>
       <c r="BO96" s="126"/>
       <c r="BP96" s="126"/>
       <c r="BQ96" s="127"/>
-      <c r="BR96" s="125"/>
+      <c r="BR96" s="125" t="s">
+        <v>28</v>
+      </c>
       <c r="BS96" s="126"/>
       <c r="BT96" s="126"/>
       <c r="BU96" s="127"/>
@@ -14968,7 +14963,7 @@
       <c r="Y97" s="12"/>
       <c r="Z97" s="12"/>
       <c r="AA97" s="14" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="AB97" s="12"/>
       <c r="AC97" s="13"/>
@@ -14998,7 +14993,7 @@
       <c r="AY97" s="12"/>
       <c r="AZ97" s="12"/>
       <c r="BA97" s="11" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="BB97" s="10"/>
       <c r="BC97" s="10"/>
@@ -15074,9 +15069,7 @@
       <c r="AX98" s="12"/>
       <c r="AY98" s="12"/>
       <c r="AZ98" s="12"/>
-      <c r="BA98" s="11" t="s">
-        <v>174</v>
-      </c>
+      <c r="BA98" s="11"/>
       <c r="BB98" s="10"/>
       <c r="BC98" s="10"/>
       <c r="BD98" s="10"/>
@@ -15151,9 +15144,7 @@
       <c r="AX99" s="5"/>
       <c r="AY99" s="5"/>
       <c r="AZ99" s="5"/>
-      <c r="BA99" s="4" t="s">
-        <v>188</v>
-      </c>
+      <c r="BA99" s="4"/>
       <c r="BB99" s="3"/>
       <c r="BC99" s="3"/>
       <c r="BD99" s="3"/>
@@ -15245,7 +15236,7 @@
       <c r="AY100" s="12"/>
       <c r="AZ100" s="12"/>
       <c r="BA100" s="11" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="BB100" s="10"/>
       <c r="BC100" s="10"/>
@@ -15256,14 +15247,20 @@
       <c r="BH100" s="10"/>
       <c r="BI100" s="12"/>
       <c r="BJ100" s="12"/>
-      <c r="BK100" s="125"/>
+      <c r="BK100" s="125" t="s">
+        <v>185</v>
+      </c>
       <c r="BL100" s="126"/>
       <c r="BM100" s="127"/>
-      <c r="BN100" s="125"/>
+      <c r="BN100" s="134">
+        <v>45586</v>
+      </c>
       <c r="BO100" s="126"/>
       <c r="BP100" s="126"/>
       <c r="BQ100" s="127"/>
-      <c r="BR100" s="125"/>
+      <c r="BR100" s="125" t="s">
+        <v>28</v>
+      </c>
       <c r="BS100" s="126"/>
       <c r="BT100" s="126"/>
       <c r="BU100" s="127"/>
@@ -15296,7 +15293,7 @@
       <c r="Y101" s="12"/>
       <c r="Z101" s="12"/>
       <c r="AA101" s="14" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="AB101" s="12"/>
       <c r="AC101" s="13"/>
@@ -15326,7 +15323,7 @@
       <c r="AY101" s="12"/>
       <c r="AZ101" s="12"/>
       <c r="BA101" s="11" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="BB101" s="10"/>
       <c r="BC101" s="10"/>
@@ -15402,9 +15399,7 @@
       <c r="AX102" s="12"/>
       <c r="AY102" s="12"/>
       <c r="AZ102" s="12"/>
-      <c r="BA102" s="11" t="s">
-        <v>174</v>
-      </c>
+      <c r="BA102" s="11"/>
       <c r="BB102" s="10"/>
       <c r="BC102" s="10"/>
       <c r="BD102" s="10"/>
@@ -15479,9 +15474,7 @@
       <c r="AX103" s="5"/>
       <c r="AY103" s="5"/>
       <c r="AZ103" s="5"/>
-      <c r="BA103" s="4" t="s">
-        <v>188</v>
-      </c>
+      <c r="BA103" s="4"/>
       <c r="BB103" s="3"/>
       <c r="BC103" s="3"/>
       <c r="BD103" s="3"/>
@@ -15573,7 +15566,7 @@
       <c r="AY104" s="12"/>
       <c r="AZ104" s="12"/>
       <c r="BA104" s="11" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="BB104" s="10"/>
       <c r="BC104" s="10"/>
@@ -15584,14 +15577,20 @@
       <c r="BH104" s="10"/>
       <c r="BI104" s="12"/>
       <c r="BJ104" s="12"/>
-      <c r="BK104" s="125"/>
+      <c r="BK104" s="125" t="s">
+        <v>185</v>
+      </c>
       <c r="BL104" s="126"/>
       <c r="BM104" s="127"/>
-      <c r="BN104" s="125"/>
+      <c r="BN104" s="134">
+        <v>45586</v>
+      </c>
       <c r="BO104" s="126"/>
       <c r="BP104" s="126"/>
       <c r="BQ104" s="127"/>
-      <c r="BR104" s="125"/>
+      <c r="BR104" s="125" t="s">
+        <v>28</v>
+      </c>
       <c r="BS104" s="126"/>
       <c r="BT104" s="126"/>
       <c r="BU104" s="127"/>
@@ -15624,7 +15623,7 @@
       <c r="Y105" s="12"/>
       <c r="Z105" s="12"/>
       <c r="AA105" s="14" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="AB105" s="12"/>
       <c r="AC105" s="13"/>
@@ -15654,7 +15653,7 @@
       <c r="AY105" s="12"/>
       <c r="AZ105" s="12"/>
       <c r="BA105" s="11" t="s">
-        <v>173</v>
+        <v>187</v>
       </c>
       <c r="BB105" s="10"/>
       <c r="BC105" s="10"/>
@@ -15730,9 +15729,7 @@
       <c r="AX106" s="12"/>
       <c r="AY106" s="12"/>
       <c r="AZ106" s="12"/>
-      <c r="BA106" s="11" t="s">
-        <v>174</v>
-      </c>
+      <c r="BA106" s="11"/>
       <c r="BB106" s="10"/>
       <c r="BC106" s="10"/>
       <c r="BD106" s="10"/>
@@ -15807,9 +15804,7 @@
       <c r="AX107" s="5"/>
       <c r="AY107" s="5"/>
       <c r="AZ107" s="5"/>
-      <c r="BA107" s="4" t="s">
-        <v>188</v>
-      </c>
+      <c r="BA107" s="4"/>
       <c r="BB107" s="3"/>
       <c r="BC107" s="3"/>
       <c r="BD107" s="3"/>
@@ -44708,17 +44703,75 @@
     </row>
   </sheetData>
   <mergeCells count="96">
-    <mergeCell ref="BK80:BM83"/>
-    <mergeCell ref="BN80:BQ83"/>
-    <mergeCell ref="BR80:BU83"/>
-    <mergeCell ref="BK84:BM87"/>
-    <mergeCell ref="BN84:BQ87"/>
-    <mergeCell ref="BR84:BU87"/>
-    <mergeCell ref="BN72:BQ75"/>
-    <mergeCell ref="BR72:BU75"/>
-    <mergeCell ref="BK76:BM79"/>
-    <mergeCell ref="BN76:BQ79"/>
-    <mergeCell ref="BR76:BU79"/>
+    <mergeCell ref="BK100:BM103"/>
+    <mergeCell ref="BN100:BQ103"/>
+    <mergeCell ref="BR100:BU103"/>
+    <mergeCell ref="BK104:BM107"/>
+    <mergeCell ref="BN104:BQ107"/>
+    <mergeCell ref="BR104:BU107"/>
+    <mergeCell ref="BK92:BM95"/>
+    <mergeCell ref="BN92:BQ95"/>
+    <mergeCell ref="BR92:BU95"/>
+    <mergeCell ref="BK96:BM99"/>
+    <mergeCell ref="BN96:BQ99"/>
+    <mergeCell ref="BR96:BU99"/>
+    <mergeCell ref="A5:B6"/>
+    <mergeCell ref="C5:F6"/>
+    <mergeCell ref="AA5:AN6"/>
+    <mergeCell ref="A1:R2"/>
+    <mergeCell ref="S1:AB1"/>
+    <mergeCell ref="AC1:AL1"/>
+    <mergeCell ref="AM1:AP1"/>
+    <mergeCell ref="U5:Z6"/>
+    <mergeCell ref="BC1:BF2"/>
+    <mergeCell ref="S2:AB2"/>
+    <mergeCell ref="AC2:AL2"/>
+    <mergeCell ref="AM2:AP2"/>
+    <mergeCell ref="AQ2:AZ2"/>
+    <mergeCell ref="AQ1:AZ1"/>
+    <mergeCell ref="BA1:BB2"/>
+    <mergeCell ref="BK5:BM6"/>
+    <mergeCell ref="BA5:BJ6"/>
+    <mergeCell ref="BN5:BQ6"/>
+    <mergeCell ref="BR5:BU6"/>
+    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="O6:T6"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="AO5:AZ6"/>
+    <mergeCell ref="BK7:BM10"/>
+    <mergeCell ref="BN7:BQ10"/>
+    <mergeCell ref="BR7:BU10"/>
+    <mergeCell ref="BK11:BM14"/>
+    <mergeCell ref="BN11:BQ14"/>
+    <mergeCell ref="BR11:BU14"/>
+    <mergeCell ref="BK15:BM18"/>
+    <mergeCell ref="BN15:BQ18"/>
+    <mergeCell ref="BR15:BU18"/>
+    <mergeCell ref="BK19:BM22"/>
+    <mergeCell ref="BN19:BQ22"/>
+    <mergeCell ref="BR19:BU22"/>
+    <mergeCell ref="BK23:BM26"/>
+    <mergeCell ref="BN23:BQ26"/>
+    <mergeCell ref="BR23:BU26"/>
+    <mergeCell ref="BK27:BM30"/>
+    <mergeCell ref="BN27:BQ30"/>
+    <mergeCell ref="BR27:BU30"/>
+    <mergeCell ref="BK52:BM55"/>
+    <mergeCell ref="BN52:BQ55"/>
+    <mergeCell ref="BR52:BU55"/>
+    <mergeCell ref="BK31:BM34"/>
+    <mergeCell ref="BN31:BQ34"/>
+    <mergeCell ref="BR31:BU34"/>
+    <mergeCell ref="BK35:BM43"/>
+    <mergeCell ref="BN35:BQ43"/>
+    <mergeCell ref="BR35:BU43"/>
+    <mergeCell ref="BK56:BM59"/>
+    <mergeCell ref="BN56:BQ59"/>
+    <mergeCell ref="BR56:BU59"/>
+    <mergeCell ref="BK60:BM63"/>
+    <mergeCell ref="BN60:BQ63"/>
+    <mergeCell ref="BR60:BU63"/>
     <mergeCell ref="BK88:BM91"/>
     <mergeCell ref="BN88:BQ91"/>
     <mergeCell ref="BR88:BU91"/>
@@ -44735,75 +44788,17 @@
     <mergeCell ref="BN68:BQ71"/>
     <mergeCell ref="BR68:BU71"/>
     <mergeCell ref="BK72:BM75"/>
-    <mergeCell ref="BK56:BM59"/>
-    <mergeCell ref="BN56:BQ59"/>
-    <mergeCell ref="BR56:BU59"/>
-    <mergeCell ref="BK60:BM63"/>
-    <mergeCell ref="BN60:BQ63"/>
-    <mergeCell ref="BR60:BU63"/>
-    <mergeCell ref="BK52:BM55"/>
-    <mergeCell ref="BN52:BQ55"/>
-    <mergeCell ref="BR52:BU55"/>
-    <mergeCell ref="BK31:BM34"/>
-    <mergeCell ref="BN31:BQ34"/>
-    <mergeCell ref="BR31:BU34"/>
-    <mergeCell ref="BK35:BM43"/>
-    <mergeCell ref="BN35:BQ43"/>
-    <mergeCell ref="BR35:BU43"/>
-    <mergeCell ref="BK23:BM26"/>
-    <mergeCell ref="BN23:BQ26"/>
-    <mergeCell ref="BR23:BU26"/>
-    <mergeCell ref="BK27:BM30"/>
-    <mergeCell ref="BN27:BQ30"/>
-    <mergeCell ref="BR27:BU30"/>
-    <mergeCell ref="BK15:BM18"/>
-    <mergeCell ref="BN15:BQ18"/>
-    <mergeCell ref="BR15:BU18"/>
-    <mergeCell ref="BK19:BM22"/>
-    <mergeCell ref="BN19:BQ22"/>
-    <mergeCell ref="BR19:BU22"/>
-    <mergeCell ref="BK7:BM10"/>
-    <mergeCell ref="BN7:BQ10"/>
-    <mergeCell ref="BR7:BU10"/>
-    <mergeCell ref="BK11:BM14"/>
-    <mergeCell ref="BN11:BQ14"/>
-    <mergeCell ref="BR11:BU14"/>
-    <mergeCell ref="BK5:BM6"/>
-    <mergeCell ref="BA5:BJ6"/>
-    <mergeCell ref="BN5:BQ6"/>
-    <mergeCell ref="BR5:BU6"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="O6:T6"/>
-    <mergeCell ref="K6:N6"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="AO5:AZ6"/>
-    <mergeCell ref="BC1:BF2"/>
-    <mergeCell ref="S2:AB2"/>
-    <mergeCell ref="AC2:AL2"/>
-    <mergeCell ref="AM2:AP2"/>
-    <mergeCell ref="AQ2:AZ2"/>
-    <mergeCell ref="AQ1:AZ1"/>
-    <mergeCell ref="BA1:BB2"/>
-    <mergeCell ref="A5:B6"/>
-    <mergeCell ref="C5:F6"/>
-    <mergeCell ref="AA5:AN6"/>
-    <mergeCell ref="A1:R2"/>
-    <mergeCell ref="S1:AB1"/>
-    <mergeCell ref="AC1:AL1"/>
-    <mergeCell ref="AM1:AP1"/>
-    <mergeCell ref="U5:Z6"/>
-    <mergeCell ref="BK92:BM95"/>
-    <mergeCell ref="BN92:BQ95"/>
-    <mergeCell ref="BR92:BU95"/>
-    <mergeCell ref="BK96:BM99"/>
-    <mergeCell ref="BN96:BQ99"/>
-    <mergeCell ref="BR96:BU99"/>
-    <mergeCell ref="BK100:BM103"/>
-    <mergeCell ref="BN100:BQ103"/>
-    <mergeCell ref="BR100:BU103"/>
-    <mergeCell ref="BK104:BM107"/>
-    <mergeCell ref="BN104:BQ107"/>
-    <mergeCell ref="BR104:BU107"/>
+    <mergeCell ref="BN72:BQ75"/>
+    <mergeCell ref="BR72:BU75"/>
+    <mergeCell ref="BK76:BM79"/>
+    <mergeCell ref="BN76:BQ79"/>
+    <mergeCell ref="BR76:BU79"/>
+    <mergeCell ref="BK80:BM83"/>
+    <mergeCell ref="BN80:BQ83"/>
+    <mergeCell ref="BR80:BU83"/>
+    <mergeCell ref="BK84:BM87"/>
+    <mergeCell ref="BN84:BQ87"/>
+    <mergeCell ref="BR84:BU87"/>
   </mergeCells>
   <phoneticPr fontId="5"/>
   <pageMargins left="0.59055118110236227" right="0.39370078740157483" top="0.59055118110236227" bottom="0.59055118110236227" header="0.39370078740157483" footer="0.39370078740157483"/>
@@ -44829,60 +44824,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="13.8" customHeight="1" thickTop="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="120"/>
-      <c r="C1" s="120"/>
-      <c r="D1" s="160" t="s">
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="162" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="161"/>
-      <c r="F1" s="167"/>
-      <c r="G1" s="168"/>
-      <c r="H1" s="169"/>
-      <c r="I1" s="160" t="s">
+      <c r="E1" s="163"/>
+      <c r="F1" s="175"/>
+      <c r="G1" s="176"/>
+      <c r="H1" s="177"/>
+      <c r="I1" s="162" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="161"/>
-      <c r="K1" s="172">
+      <c r="J1" s="163"/>
+      <c r="K1" s="166">
         <v>45567</v>
       </c>
-      <c r="L1" s="173"/>
+      <c r="L1" s="167"/>
       <c r="M1" s="85">
         <v>45568</v>
       </c>
-      <c r="N1" s="176" t="s">
+      <c r="N1" s="170" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="170"/>
+      <c r="O1" s="160"/>
     </row>
     <row r="2" spans="1:15" ht="13.8" customHeight="1" thickBot="1">
-      <c r="A2" s="122"/>
-      <c r="B2" s="123"/>
-      <c r="C2" s="123"/>
-      <c r="D2" s="162" t="s">
+      <c r="A2" s="109"/>
+      <c r="B2" s="110"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="164" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="163"/>
-      <c r="F2" s="164" t="s">
+      <c r="E2" s="165"/>
+      <c r="F2" s="172" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="165"/>
-      <c r="H2" s="166"/>
-      <c r="I2" s="162" t="s">
+      <c r="G2" s="173"/>
+      <c r="H2" s="174"/>
+      <c r="I2" s="164" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="163"/>
-      <c r="K2" s="174" t="s">
+      <c r="J2" s="165"/>
+      <c r="K2" s="168" t="s">
         <v>28</v>
       </c>
-      <c r="L2" s="175"/>
+      <c r="L2" s="169"/>
       <c r="M2" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="N2" s="177"/>
-      <c r="O2" s="171"/>
+      <c r="N2" s="171"/>
+      <c r="O2" s="161"/>
     </row>
     <row r="3" spans="1:15" ht="13.8" thickTop="1">
       <c r="A3" s="81" t="s">
@@ -45432,17 +45427,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="F1:H1"/>
     <mergeCell ref="O1:O2"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K1:L1"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="N1:N2"/>
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="F1:H1"/>
   </mergeCells>
   <phoneticPr fontId="5"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -45461,60 +45456,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="13.8" thickTop="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="120"/>
-      <c r="C1" s="120"/>
-      <c r="D1" s="160" t="s">
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="162" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="161"/>
-      <c r="F1" s="167"/>
-      <c r="G1" s="168"/>
-      <c r="H1" s="169"/>
-      <c r="I1" s="160" t="s">
+      <c r="E1" s="163"/>
+      <c r="F1" s="175"/>
+      <c r="G1" s="176"/>
+      <c r="H1" s="177"/>
+      <c r="I1" s="162" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="161"/>
-      <c r="K1" s="172">
+      <c r="J1" s="163"/>
+      <c r="K1" s="166">
         <v>45567</v>
       </c>
-      <c r="L1" s="173"/>
+      <c r="L1" s="167"/>
       <c r="M1" s="85">
         <v>45568</v>
       </c>
-      <c r="N1" s="176" t="s">
+      <c r="N1" s="170" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="170"/>
+      <c r="O1" s="160"/>
     </row>
     <row r="2" spans="1:15" ht="13.8" thickBot="1">
-      <c r="A2" s="122"/>
-      <c r="B2" s="123"/>
-      <c r="C2" s="123"/>
-      <c r="D2" s="162" t="s">
+      <c r="A2" s="109"/>
+      <c r="B2" s="110"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="164" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="163"/>
-      <c r="F2" s="164" t="s">
+      <c r="E2" s="165"/>
+      <c r="F2" s="172" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="165"/>
-      <c r="H2" s="166"/>
-      <c r="I2" s="162" t="s">
+      <c r="G2" s="173"/>
+      <c r="H2" s="174"/>
+      <c r="I2" s="164" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="163"/>
-      <c r="K2" s="174" t="s">
+      <c r="J2" s="165"/>
+      <c r="K2" s="168" t="s">
         <v>28</v>
       </c>
-      <c r="L2" s="175"/>
+      <c r="L2" s="169"/>
       <c r="M2" s="66" t="s">
         <v>28</v>
       </c>
-      <c r="N2" s="177"/>
-      <c r="O2" s="171"/>
+      <c r="N2" s="171"/>
+      <c r="O2" s="161"/>
     </row>
     <row r="3" spans="1:15" ht="13.8" thickTop="1">
       <c r="A3" s="81" t="s">
@@ -45826,6 +45821,353 @@
       </c>
       <c r="H14" s="79" t="b">
         <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="O1:O2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="N1:N2"/>
+  </mergeCells>
+  <phoneticPr fontId="5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6DE800-A6D7-4C58-87F6-B3B66BE74E72}">
+  <dimension ref="A1:O12"/>
+  <sheetFormatPr defaultRowHeight="13.2"/>
+  <cols>
+    <col min="1" max="1" width="8.88671875" customWidth="1"/>
+    <col min="2" max="2" width="21.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="13.8" thickTop="1">
+      <c r="A1" s="106" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="162" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" s="163"/>
+      <c r="F1" s="178"/>
+      <c r="G1" s="179"/>
+      <c r="H1" s="180"/>
+      <c r="I1" s="162" t="s">
+        <v>14</v>
+      </c>
+      <c r="J1" s="163"/>
+      <c r="K1" s="166">
+        <v>45567</v>
+      </c>
+      <c r="L1" s="167"/>
+      <c r="M1" s="85">
+        <v>45568</v>
+      </c>
+      <c r="N1" s="170" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="160"/>
+    </row>
+    <row r="2" spans="1:15" ht="13.8" thickBot="1">
+      <c r="A2" s="109"/>
+      <c r="B2" s="110"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="164" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="165"/>
+      <c r="F2" s="172" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="173"/>
+      <c r="H2" s="174"/>
+      <c r="I2" s="164" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="165"/>
+      <c r="K2" s="168" t="s">
+        <v>28</v>
+      </c>
+      <c r="L2" s="169"/>
+      <c r="M2" s="67" t="s">
+        <v>28</v>
+      </c>
+      <c r="N2" s="171"/>
+      <c r="O2" s="161"/>
+    </row>
+    <row r="3" spans="1:15" ht="13.8" thickTop="1">
+      <c r="A3" s="81" t="s">
+        <v>93</v>
+      </c>
+      <c r="B3" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="C3" s="69" t="s">
+        <v>46</v>
+      </c>
+      <c r="D3" s="70" t="s">
+        <v>47</v>
+      </c>
+      <c r="E3" s="69" t="s">
+        <v>48</v>
+      </c>
+      <c r="F3" s="70" t="s">
+        <v>49</v>
+      </c>
+      <c r="G3" s="69" t="s">
+        <v>50</v>
+      </c>
+      <c r="H3" s="71" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
+      <c r="A4" s="83">
+        <v>1</v>
+      </c>
+      <c r="B4" s="72" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" s="73" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" s="74">
+        <v>2</v>
+      </c>
+      <c r="E4" s="73" t="s">
+        <v>62</v>
+      </c>
+      <c r="F4" s="74">
+        <v>1980</v>
+      </c>
+      <c r="G4" s="73">
+        <v>18</v>
+      </c>
+      <c r="H4" s="75" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" s="83">
+        <v>2</v>
+      </c>
+      <c r="B5" s="72" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="73" t="s">
+        <v>73</v>
+      </c>
+      <c r="D5" s="74">
+        <v>2</v>
+      </c>
+      <c r="E5" s="73" t="s">
+        <v>64</v>
+      </c>
+      <c r="F5" s="74">
+        <v>4980</v>
+      </c>
+      <c r="G5" s="73">
+        <v>15</v>
+      </c>
+      <c r="H5" s="75" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" s="83">
+        <v>3</v>
+      </c>
+      <c r="B6" s="72" t="s">
+        <v>75</v>
+      </c>
+      <c r="C6" s="73" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" s="74">
+        <v>2</v>
+      </c>
+      <c r="E6" s="73" t="s">
+        <v>66</v>
+      </c>
+      <c r="F6" s="74">
+        <v>2200</v>
+      </c>
+      <c r="G6" s="73">
+        <v>3</v>
+      </c>
+      <c r="H6" s="75" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" s="83">
+        <v>4</v>
+      </c>
+      <c r="B7" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="C7" s="73" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" s="74">
+        <v>2</v>
+      </c>
+      <c r="E7" s="73" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" s="74">
+        <v>2980</v>
+      </c>
+      <c r="G7" s="73">
+        <v>6</v>
+      </c>
+      <c r="H7" s="75" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" s="83">
+        <v>5</v>
+      </c>
+      <c r="B8" s="72" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="73" t="s">
+        <v>78</v>
+      </c>
+      <c r="D8" s="74">
+        <v>2</v>
+      </c>
+      <c r="E8" s="73" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8" s="74">
+        <v>780</v>
+      </c>
+      <c r="G8" s="73">
+        <v>17</v>
+      </c>
+      <c r="H8" s="75" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" s="83">
+        <v>6</v>
+      </c>
+      <c r="B9" s="72" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" s="73" t="s">
+        <v>76</v>
+      </c>
+      <c r="D9" s="74">
+        <v>2</v>
+      </c>
+      <c r="E9" s="73" t="s">
+        <v>60</v>
+      </c>
+      <c r="F9" s="74">
+        <v>2500</v>
+      </c>
+      <c r="G9" s="73">
+        <v>9</v>
+      </c>
+      <c r="H9" s="75" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" s="83">
+        <v>7</v>
+      </c>
+      <c r="B10" s="72" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" s="73" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="74">
+        <v>2</v>
+      </c>
+      <c r="E10" s="73" t="s">
+        <v>62</v>
+      </c>
+      <c r="F10" s="74">
+        <v>1800</v>
+      </c>
+      <c r="G10" s="73">
+        <v>20</v>
+      </c>
+      <c r="H10" s="75" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" s="83">
+        <v>8</v>
+      </c>
+      <c r="B11" s="72" t="s">
+        <v>82</v>
+      </c>
+      <c r="C11" s="73" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" s="74">
+        <v>2</v>
+      </c>
+      <c r="E11" s="73" t="s">
+        <v>64</v>
+      </c>
+      <c r="F11" s="74">
+        <v>1980</v>
+      </c>
+      <c r="G11" s="73">
+        <v>2</v>
+      </c>
+      <c r="H11" s="75" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" s="84">
+        <v>9</v>
+      </c>
+      <c r="B12" s="76" t="s">
+        <v>83</v>
+      </c>
+      <c r="C12" s="77" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" s="78">
+        <v>2</v>
+      </c>
+      <c r="E12" s="77" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" s="78">
+        <v>690</v>
+      </c>
+      <c r="G12" s="77">
+        <v>1</v>
+      </c>
+      <c r="H12" s="79" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -45847,353 +46189,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4D6DE800-A6D7-4C58-87F6-B3B66BE74E72}">
-  <dimension ref="A1:O12"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
-  <cols>
-    <col min="1" max="1" width="8.88671875" customWidth="1"/>
-    <col min="2" max="2" width="21.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:15" ht="13.8" thickTop="1">
-      <c r="A1" s="119" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="120"/>
-      <c r="C1" s="120"/>
-      <c r="D1" s="160" t="s">
-        <v>15</v>
-      </c>
-      <c r="E1" s="161"/>
-      <c r="F1" s="178"/>
-      <c r="G1" s="179"/>
-      <c r="H1" s="180"/>
-      <c r="I1" s="160" t="s">
-        <v>14</v>
-      </c>
-      <c r="J1" s="161"/>
-      <c r="K1" s="172">
-        <v>45567</v>
-      </c>
-      <c r="L1" s="173"/>
-      <c r="M1" s="85">
-        <v>45568</v>
-      </c>
-      <c r="N1" s="176" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="170"/>
-    </row>
-    <row r="2" spans="1:15" ht="13.8" thickBot="1">
-      <c r="A2" s="122"/>
-      <c r="B2" s="123"/>
-      <c r="C2" s="123"/>
-      <c r="D2" s="162" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="163"/>
-      <c r="F2" s="164" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="165"/>
-      <c r="H2" s="166"/>
-      <c r="I2" s="162" t="s">
-        <v>10</v>
-      </c>
-      <c r="J2" s="163"/>
-      <c r="K2" s="174" t="s">
-        <v>28</v>
-      </c>
-      <c r="L2" s="175"/>
-      <c r="M2" s="67" t="s">
-        <v>28</v>
-      </c>
-      <c r="N2" s="177"/>
-      <c r="O2" s="171"/>
-    </row>
-    <row r="3" spans="1:15" ht="13.8" thickTop="1">
-      <c r="A3" s="81" t="s">
-        <v>93</v>
-      </c>
-      <c r="B3" s="68" t="s">
-        <v>45</v>
-      </c>
-      <c r="C3" s="69" t="s">
-        <v>46</v>
-      </c>
-      <c r="D3" s="70" t="s">
-        <v>47</v>
-      </c>
-      <c r="E3" s="69" t="s">
-        <v>48</v>
-      </c>
-      <c r="F3" s="70" t="s">
-        <v>49</v>
-      </c>
-      <c r="G3" s="69" t="s">
-        <v>50</v>
-      </c>
-      <c r="H3" s="71" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
-      <c r="A4" s="83">
-        <v>1</v>
-      </c>
-      <c r="B4" s="72" t="s">
-        <v>72</v>
-      </c>
-      <c r="C4" s="73" t="s">
-        <v>73</v>
-      </c>
-      <c r="D4" s="74">
-        <v>2</v>
-      </c>
-      <c r="E4" s="73" t="s">
-        <v>62</v>
-      </c>
-      <c r="F4" s="74">
-        <v>1980</v>
-      </c>
-      <c r="G4" s="73">
-        <v>18</v>
-      </c>
-      <c r="H4" s="75" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
-      <c r="A5" s="83">
-        <v>2</v>
-      </c>
-      <c r="B5" s="72" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" s="73" t="s">
-        <v>73</v>
-      </c>
-      <c r="D5" s="74">
-        <v>2</v>
-      </c>
-      <c r="E5" s="73" t="s">
-        <v>64</v>
-      </c>
-      <c r="F5" s="74">
-        <v>4980</v>
-      </c>
-      <c r="G5" s="73">
-        <v>15</v>
-      </c>
-      <c r="H5" s="75" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="A6" s="83">
-        <v>3</v>
-      </c>
-      <c r="B6" s="72" t="s">
-        <v>75</v>
-      </c>
-      <c r="C6" s="73" t="s">
-        <v>76</v>
-      </c>
-      <c r="D6" s="74">
-        <v>2</v>
-      </c>
-      <c r="E6" s="73" t="s">
-        <v>66</v>
-      </c>
-      <c r="F6" s="74">
-        <v>2200</v>
-      </c>
-      <c r="G6" s="73">
-        <v>3</v>
-      </c>
-      <c r="H6" s="75" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
-      <c r="A7" s="83">
-        <v>4</v>
-      </c>
-      <c r="B7" s="72" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" s="73" t="s">
-        <v>78</v>
-      </c>
-      <c r="D7" s="74">
-        <v>2</v>
-      </c>
-      <c r="E7" s="73" t="s">
-        <v>54</v>
-      </c>
-      <c r="F7" s="74">
-        <v>2980</v>
-      </c>
-      <c r="G7" s="73">
-        <v>6</v>
-      </c>
-      <c r="H7" s="75" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
-      <c r="A8" s="83">
-        <v>5</v>
-      </c>
-      <c r="B8" s="72" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" s="73" t="s">
-        <v>78</v>
-      </c>
-      <c r="D8" s="74">
-        <v>2</v>
-      </c>
-      <c r="E8" s="73" t="s">
-        <v>57</v>
-      </c>
-      <c r="F8" s="74">
-        <v>780</v>
-      </c>
-      <c r="G8" s="73">
-        <v>17</v>
-      </c>
-      <c r="H8" s="75" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
-      <c r="A9" s="83">
-        <v>6</v>
-      </c>
-      <c r="B9" s="72" t="s">
-        <v>80</v>
-      </c>
-      <c r="C9" s="73" t="s">
-        <v>76</v>
-      </c>
-      <c r="D9" s="74">
-        <v>2</v>
-      </c>
-      <c r="E9" s="73" t="s">
-        <v>60</v>
-      </c>
-      <c r="F9" s="74">
-        <v>2500</v>
-      </c>
-      <c r="G9" s="73">
-        <v>9</v>
-      </c>
-      <c r="H9" s="75" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
-      <c r="A10" s="83">
-        <v>7</v>
-      </c>
-      <c r="B10" s="72" t="s">
-        <v>81</v>
-      </c>
-      <c r="C10" s="73" t="s">
-        <v>73</v>
-      </c>
-      <c r="D10" s="74">
-        <v>2</v>
-      </c>
-      <c r="E10" s="73" t="s">
-        <v>62</v>
-      </c>
-      <c r="F10" s="74">
-        <v>1800</v>
-      </c>
-      <c r="G10" s="73">
-        <v>20</v>
-      </c>
-      <c r="H10" s="75" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
-      <c r="A11" s="83">
-        <v>8</v>
-      </c>
-      <c r="B11" s="72" t="s">
-        <v>82</v>
-      </c>
-      <c r="C11" s="73" t="s">
-        <v>73</v>
-      </c>
-      <c r="D11" s="74">
-        <v>2</v>
-      </c>
-      <c r="E11" s="73" t="s">
-        <v>64</v>
-      </c>
-      <c r="F11" s="74">
-        <v>1980</v>
-      </c>
-      <c r="G11" s="73">
-        <v>2</v>
-      </c>
-      <c r="H11" s="75" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
-      <c r="A12" s="84">
-        <v>9</v>
-      </c>
-      <c r="B12" s="76" t="s">
-        <v>83</v>
-      </c>
-      <c r="C12" s="77" t="s">
-        <v>78</v>
-      </c>
-      <c r="D12" s="78">
-        <v>2</v>
-      </c>
-      <c r="E12" s="77" t="s">
-        <v>57</v>
-      </c>
-      <c r="F12" s="78">
-        <v>690</v>
-      </c>
-      <c r="G12" s="77">
-        <v>1</v>
-      </c>
-      <c r="H12" s="79" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="O1:O2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="N1:N2"/>
-  </mergeCells>
-  <phoneticPr fontId="5"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C301507-5DEA-4412-B922-D11B8196CBA9}">
   <dimension ref="A1:O3"/>
@@ -46206,60 +46201,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="13.8" customHeight="1" thickTop="1">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="106" t="s">
         <v>16</v>
       </c>
-      <c r="B1" s="120"/>
-      <c r="C1" s="120"/>
-      <c r="D1" s="160" t="s">
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="162" t="s">
         <v>15</v>
       </c>
-      <c r="E1" s="161"/>
-      <c r="F1" s="167"/>
-      <c r="G1" s="168"/>
-      <c r="H1" s="169"/>
-      <c r="I1" s="160" t="s">
+      <c r="E1" s="163"/>
+      <c r="F1" s="175"/>
+      <c r="G1" s="176"/>
+      <c r="H1" s="177"/>
+      <c r="I1" s="162" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="161"/>
-      <c r="K1" s="172">
+      <c r="J1" s="163"/>
+      <c r="K1" s="166">
         <v>45567</v>
       </c>
-      <c r="L1" s="173"/>
+      <c r="L1" s="167"/>
       <c r="M1" s="85">
         <v>45568</v>
       </c>
-      <c r="N1" s="176" t="s">
+      <c r="N1" s="170" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="170"/>
+      <c r="O1" s="160"/>
     </row>
     <row r="2" spans="1:15" ht="13.8" customHeight="1" thickBot="1">
-      <c r="A2" s="122"/>
-      <c r="B2" s="123"/>
-      <c r="C2" s="123"/>
-      <c r="D2" s="162" t="s">
+      <c r="A2" s="109"/>
+      <c r="B2" s="110"/>
+      <c r="C2" s="110"/>
+      <c r="D2" s="164" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="163"/>
-      <c r="F2" s="164" t="s">
+      <c r="E2" s="165"/>
+      <c r="F2" s="172" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="165"/>
-      <c r="H2" s="166"/>
-      <c r="I2" s="162" t="s">
+      <c r="G2" s="173"/>
+      <c r="H2" s="174"/>
+      <c r="I2" s="164" t="s">
         <v>10</v>
       </c>
-      <c r="J2" s="163"/>
-      <c r="K2" s="174" t="s">
+      <c r="J2" s="165"/>
+      <c r="K2" s="168" t="s">
         <v>28</v>
       </c>
-      <c r="L2" s="175"/>
+      <c r="L2" s="169"/>
       <c r="M2" s="67" t="s">
         <v>28</v>
       </c>
-      <c r="N2" s="177"/>
-      <c r="O2" s="171"/>
+      <c r="N2" s="171"/>
+      <c r="O2" s="161"/>
     </row>
     <row r="3" spans="1:15" ht="13.8" customHeight="1" thickTop="1">
       <c r="A3" s="93" t="s">
@@ -46282,17 +46277,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="K1:L1"/>
     <mergeCell ref="O1:O2"/>
     <mergeCell ref="D2:E2"/>
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="I2:J2"/>
     <mergeCell ref="K2:L2"/>
     <mergeCell ref="N1:N2"/>
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="K1:L1"/>
   </mergeCells>
   <phoneticPr fontId="5"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
